--- a/WorkBot/legacy/backend/pricing/Templates/IBProduce.xlsx
+++ b/WorkBot/legacy/backend/pricing/Templates/IBProduce.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andrew\Desktop\Andrew\Projects\RandomStuff\WorkBot\main\backend\pricing\Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andrew\Desktop\Andrew\Projects\IthacaBakery\RandomStuff\WorkBot\legacy\backend\pricing\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36545FD9-77EB-4315-8DE6-130C0EA4816B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C26C4C2B-4CA9-42D3-BF42-89DA43FA1F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7440" yWindow="3435" windowWidth="16200" windowHeight="9360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="241">
   <si>
     <t>Item</t>
   </si>
@@ -417,21 +417,6 @@
     <t>Squash - Zucchini (Fancy, Medium)</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>1605</t>
-  </si>
-  <si>
-    <t>855</t>
-  </si>
-  <si>
-    <t>880</t>
-  </si>
-  <si>
-    <t>BEHLOG &amp; SON, INC.</t>
-  </si>
-  <si>
     <t>Asparagus</t>
   </si>
   <si>
@@ -739,6 +724,36 @@
   </si>
   <si>
     <t>VPT</t>
+  </si>
+  <si>
+    <t>Berries - Blackberries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berries - Blueberries </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berries - Raspberries </t>
+  </si>
+  <si>
+    <t>Berries - Stawberries</t>
+  </si>
+  <si>
+    <t>FBERRASP</t>
+  </si>
+  <si>
+    <t>FBERBLUP</t>
+  </si>
+  <si>
+    <t>FBERBLK</t>
+  </si>
+  <si>
+    <t>Tomato - Sliced</t>
+  </si>
+  <si>
+    <t>0683696</t>
+  </si>
+  <si>
+    <t>PTOMSL</t>
   </si>
 </sst>
 </file>
@@ -813,7 +828,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -853,12 +868,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -916,7 +925,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1010,24 +1019,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="3" fillId="8" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="3" fillId="8" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="8" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1048,22 +1039,17 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1105,7 +1091,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -1423,17 +1408,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB101"/>
+  <dimension ref="A1:X106"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="45.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.7109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="2" style="1" customWidth="1"/>
     <col min="4" max="4" width="16.7109375" style="36" customWidth="1"/>
-    <col min="5" max="5" width="15" style="9" customWidth="1"/>
+    <col min="5" max="5" width="15" style="8" customWidth="1"/>
     <col min="6" max="6" width="13.28515625" style="8" customWidth="1"/>
     <col min="7" max="8" width="12.42578125" style="15" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="58" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="50" customWidth="1"/>
     <col min="10" max="10" width="13.5703125" style="16" customWidth="1"/>
     <col min="11" max="11" width="12.5703125" style="24" customWidth="1"/>
     <col min="12" max="12" width="12.5703125" style="5" customWidth="1"/>
@@ -1441,7 +1426,7 @@
     <col min="14" max="14" width="13.5703125" style="6" customWidth="1"/>
     <col min="15" max="15" width="13.7109375" style="25" customWidth="1"/>
     <col min="16" max="16" width="13.7109375" style="7" customWidth="1"/>
-    <col min="17" max="17" width="31.85546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="31.85546875" style="10" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14" style="10" customWidth="1"/>
     <col min="19" max="19" width="13.7109375" style="28" customWidth="1"/>
     <col min="20" max="20" width="13.7109375" style="11" customWidth="1"/>
@@ -1449,65 +1434,55 @@
     <col min="22" max="22" width="14" style="18" hidden="1" customWidth="1"/>
     <col min="23" max="23" width="13.7109375" style="30" hidden="1" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" style="19" hidden="1" customWidth="1"/>
-    <col min="25" max="25" width="14.140625" style="43" customWidth="1"/>
-    <col min="26" max="26" width="14" style="47" customWidth="1"/>
-    <col min="27" max="27" width="13.7109375" style="48" customWidth="1"/>
-    <col min="28" max="28" width="13.7109375" style="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="66" t="s">
+    <row r="1" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="81" t="s">
+      <c r="B1" s="70" t="s">
         <v>60</v>
       </c>
       <c r="C1" s="42"/>
-      <c r="D1" s="68" t="s">
+      <c r="D1" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="70" t="s">
+      <c r="E1" s="59" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="71"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="70" t="s">
+      <c r="F1" s="60"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="73"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="70" t="s">
+      <c r="J1" s="62"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="59" t="s">
         <v>65</v>
       </c>
-      <c r="N1" s="77"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="67"/>
-      <c r="Q1" s="70" t="s">
+      <c r="N1" s="66"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="59" t="s">
         <v>63</v>
       </c>
-      <c r="R1" s="79"/>
-      <c r="S1" s="80"/>
-      <c r="T1" s="67"/>
-      <c r="U1" s="70" t="s">
+      <c r="R1" s="68"/>
+      <c r="S1" s="69"/>
+      <c r="T1" s="56"/>
+      <c r="U1" s="59" t="s">
         <v>62</v>
       </c>
-      <c r="V1" s="75"/>
-      <c r="W1" s="76"/>
-      <c r="X1" s="67"/>
-      <c r="Y1" s="63" t="s">
-        <v>132</v>
-      </c>
-      <c r="Z1" s="64"/>
-      <c r="AA1" s="64"/>
-      <c r="AB1" s="65"/>
-    </row>
-    <row r="2" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="67"/>
-      <c r="B2" s="81"/>
+      <c r="V1" s="64"/>
+      <c r="W1" s="65"/>
+      <c r="X1" s="56"/>
+    </row>
+    <row r="2" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="56"/>
+      <c r="B2" s="70"/>
       <c r="C2" s="42"/>
-      <c r="D2" s="69"/>
+      <c r="D2" s="58"/>
       <c r="E2" s="21" t="s">
         <v>3</v>
       </c>
@@ -1520,7 +1495,7 @@
       <c r="H2" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="49" t="s">
         <v>3</v>
       </c>
       <c r="J2" s="2" t="s">
@@ -1568,26 +1543,15 @@
       <c r="X2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="Y2" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA2" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB2" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="8"/>
-      <c r="Q3" t="s">
-        <v>153</v>
+      <c r="L3" s="24"/>
+      <c r="M3" s="46"/>
+      <c r="Q3" s="10" t="s">
+        <v>148</v>
       </c>
       <c r="R3" s="12"/>
       <c r="S3" s="27"/>
@@ -1595,28 +1559,21 @@
       <c r="V3" s="17"/>
       <c r="W3" s="32"/>
       <c r="X3" s="31"/>
-      <c r="Y3" s="43">
-        <v>845</v>
-      </c>
-      <c r="Z3" s="44"/>
-      <c r="AA3" s="45"/>
-      <c r="AB3" s="50"/>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="E4" s="8"/>
       <c r="H4" s="22"/>
-      <c r="I4" s="58">
+      <c r="I4" s="50">
         <v>1268572</v>
       </c>
       <c r="L4" s="24"/>
-      <c r="M4">
+      <c r="M4" s="46">
         <v>6793301</v>
       </c>
-      <c r="Q4" t="s">
-        <v>154</v>
+      <c r="Q4" s="10" t="s">
+        <v>149</v>
       </c>
       <c r="R4" s="12"/>
       <c r="S4" s="27"/>
@@ -1627,24 +1584,17 @@
       <c r="V4" s="38"/>
       <c r="W4" s="32"/>
       <c r="X4" s="31"/>
-      <c r="Y4" s="43">
-        <v>1081</v>
-      </c>
-      <c r="Z4" s="44"/>
-      <c r="AA4" s="45"/>
-      <c r="AB4" s="50"/>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="8"/>
       <c r="L5" s="24"/>
-      <c r="M5" s="54"/>
+      <c r="M5" s="46"/>
       <c r="N5" s="14"/>
       <c r="O5" s="26"/>
-      <c r="Q5" t="s">
-        <v>155</v>
+      <c r="Q5" s="10" t="s">
+        <v>150</v>
       </c>
       <c r="R5" s="12"/>
       <c r="S5" s="27"/>
@@ -1655,23 +1605,21 @@
       <c r="V5" s="37"/>
       <c r="W5" s="32"/>
       <c r="X5" s="31"/>
-      <c r="AA5" s="45"/>
-      <c r="AB5" s="50"/>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="I6" s="58">
+        <v>128</v>
+      </c>
+      <c r="I6" s="50">
         <v>4418752</v>
       </c>
       <c r="L6" s="24"/>
-      <c r="M6" s="54"/>
-      <c r="Q6" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="M6" s="46"/>
+      <c r="Q6" s="10" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -1681,15 +1629,15 @@
       <c r="F7" s="9"/>
       <c r="G7" s="40"/>
       <c r="H7" s="23"/>
-      <c r="I7" s="58">
+      <c r="I7" s="50">
         <v>1254440</v>
       </c>
       <c r="K7" s="41"/>
       <c r="L7" s="16"/>
-      <c r="M7" s="54"/>
+      <c r="M7" s="46"/>
       <c r="O7" s="26"/>
-      <c r="Q7" t="s">
-        <v>157</v>
+      <c r="Q7" s="10" t="s">
+        <v>152</v>
       </c>
       <c r="R7" s="12"/>
       <c r="S7" s="27"/>
@@ -1700,2655 +1648,2421 @@
       <c r="V7" s="38"/>
       <c r="W7" s="32"/>
       <c r="X7" s="31"/>
-      <c r="Y7" s="43">
-        <v>1125</v>
-      </c>
-      <c r="Z7" s="44"/>
-      <c r="AA7" s="45"/>
-      <c r="AB7" s="50"/>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="I8" s="58">
+      <c r="I8" s="50">
         <v>7567159</v>
       </c>
       <c r="L8" s="24"/>
-      <c r="M8" s="54"/>
-      <c r="Q8" t="s">
-        <v>158</v>
-      </c>
-      <c r="Y8" s="43" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="M8" s="46"/>
+      <c r="Q8" s="10" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D9"/>
+      <c r="E9" s="54">
+        <v>78436</v>
+      </c>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="50">
+        <v>1007871</v>
+      </c>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="46"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="14"/>
+      <c r="Q9" s="51" t="s">
+        <v>237</v>
+      </c>
+      <c r="R9" s="12"/>
+      <c r="S9" s="12"/>
+      <c r="T9" s="12"/>
+      <c r="U9"/>
+      <c r="V9"/>
+      <c r="W9"/>
+      <c r="X9"/>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D10"/>
+      <c r="E10" s="54">
+        <v>77732</v>
+      </c>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="50">
+        <v>1254390</v>
+      </c>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="53">
+        <v>9502089</v>
+      </c>
+      <c r="N10" s="14"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="14"/>
+      <c r="Q10" s="51" t="s">
+        <v>236</v>
+      </c>
+      <c r="R10" s="12"/>
+      <c r="S10" s="12"/>
+      <c r="T10" s="12"/>
+      <c r="U10"/>
+      <c r="V10"/>
+      <c r="W10"/>
+      <c r="X10"/>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D11"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="50">
+        <v>1182336</v>
+      </c>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="53">
+        <v>7006455</v>
+      </c>
+      <c r="N11" s="14"/>
+      <c r="O11" s="14"/>
+      <c r="P11" s="14"/>
+      <c r="Q11" s="51" t="s">
+        <v>235</v>
+      </c>
+      <c r="R11" s="12"/>
+      <c r="S11" s="12"/>
+      <c r="T11" s="12"/>
+      <c r="U11"/>
+      <c r="V11"/>
+      <c r="W11"/>
+      <c r="X11"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D12"/>
+      <c r="E12" s="54">
+        <v>39142</v>
+      </c>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="50">
+        <v>6235501</v>
+      </c>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="53">
+        <v>1205582</v>
+      </c>
+      <c r="N12" s="14"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="14"/>
+      <c r="Q12" s="51" t="s">
+        <v>227</v>
+      </c>
+      <c r="R12" s="12"/>
+      <c r="S12" s="12"/>
+      <c r="T12" s="12"/>
+      <c r="U12"/>
+      <c r="V12"/>
+      <c r="W12"/>
+      <c r="X12"/>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="D13" s="48"/>
+      <c r="E13" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="9"/>
-      <c r="G9" s="40"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="58">
+      <c r="F13" s="9"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="50">
         <v>2704989</v>
       </c>
-      <c r="K9" s="41"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="59">
+      <c r="K13" s="41"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="53">
         <v>8355281</v>
       </c>
-      <c r="N9" s="14"/>
-      <c r="O9" s="26"/>
-      <c r="P9" s="51"/>
-      <c r="Q9" t="s">
-        <v>159</v>
-      </c>
-      <c r="S9" s="27"/>
-      <c r="T9" s="29"/>
-      <c r="U9" s="34">
+      <c r="N13" s="14"/>
+      <c r="O13" s="26"/>
+      <c r="P13" s="43"/>
+      <c r="Q13" s="51" t="s">
+        <v>154</v>
+      </c>
+      <c r="S13" s="27"/>
+      <c r="T13" s="29"/>
+      <c r="U13" s="34">
         <v>8203</v>
       </c>
-      <c r="V9" s="38"/>
-      <c r="W9" s="32"/>
-      <c r="X9" s="31"/>
-      <c r="Y9" s="43">
-        <v>45</v>
-      </c>
-      <c r="Z9" s="44"/>
-      <c r="AA9" s="45"/>
-      <c r="AB9" s="50"/>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="V13" s="38"/>
+      <c r="W13" s="32"/>
+      <c r="X13" s="31"/>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="D14" s="48"/>
+      <c r="E14" s="54" t="s">
         <v>14</v>
-      </c>
-      <c r="F10" s="9"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="23"/>
-      <c r="I10" s="58">
-        <v>1675859</v>
-      </c>
-      <c r="K10" s="41"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="59">
-        <v>2326429</v>
-      </c>
-      <c r="N10" s="14"/>
-      <c r="O10" s="26"/>
-      <c r="P10" s="51"/>
-      <c r="Q10" t="s">
-        <v>160</v>
-      </c>
-      <c r="R10" s="12"/>
-      <c r="S10" s="27"/>
-      <c r="T10" s="29"/>
-      <c r="U10" s="34">
-        <v>8893</v>
-      </c>
-      <c r="V10" s="38"/>
-      <c r="W10" s="32"/>
-      <c r="X10" s="31"/>
-      <c r="Y10" s="43">
-        <v>50</v>
-      </c>
-      <c r="Z10" s="44"/>
-      <c r="AA10" s="45"/>
-      <c r="AB10" s="50"/>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="8">
-        <v>78516</v>
-      </c>
-      <c r="F11" s="9"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="23"/>
-      <c r="I11" s="58">
-        <v>4510299</v>
-      </c>
-      <c r="K11" s="41"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="54"/>
-      <c r="O11" s="26"/>
-      <c r="Q11" t="s">
-        <v>161</v>
-      </c>
-      <c r="R11" s="12"/>
-      <c r="S11" s="27"/>
-      <c r="T11" s="29"/>
-      <c r="U11" s="34">
-        <v>8227</v>
-      </c>
-      <c r="V11" s="38"/>
-      <c r="W11" s="32"/>
-      <c r="X11" s="31"/>
-      <c r="Y11" s="43">
-        <v>53</v>
-      </c>
-      <c r="Z11" s="44"/>
-      <c r="AA11" s="45"/>
-      <c r="AB11" s="50"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="L12" s="24"/>
-      <c r="M12" s="54"/>
-      <c r="Q12"/>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="L13" s="24"/>
-      <c r="M13" s="54"/>
-      <c r="Q13"/>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>18</v>
       </c>
       <c r="F14" s="9"/>
       <c r="G14" s="40"/>
       <c r="H14" s="23"/>
-      <c r="I14" s="58">
-        <v>2227007</v>
+      <c r="I14" s="50">
+        <v>1675859</v>
       </c>
       <c r="K14" s="41"/>
       <c r="L14" s="16"/>
-      <c r="M14" s="55">
-        <v>9228446</v>
+      <c r="M14" s="53">
+        <v>2326429</v>
       </c>
       <c r="N14" s="14"/>
       <c r="O14" s="26"/>
-      <c r="P14" s="51"/>
-      <c r="Q14" t="s">
-        <v>162</v>
+      <c r="P14" s="43"/>
+      <c r="Q14" s="51" t="s">
+        <v>155</v>
       </c>
       <c r="R14" s="12"/>
       <c r="S14" s="27"/>
       <c r="T14" s="29"/>
       <c r="U14" s="34">
-        <v>8104</v>
+        <v>8893</v>
       </c>
       <c r="V14" s="38"/>
       <c r="W14" s="32"/>
       <c r="X14" s="31"/>
-      <c r="Y14" s="43">
-        <v>80</v>
-      </c>
-      <c r="Z14" s="44"/>
-      <c r="AA14" s="45"/>
-      <c r="AB14" s="50"/>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>20</v>
+        <v>15</v>
+      </c>
+      <c r="D15" s="48"/>
+      <c r="E15" s="54">
+        <v>78516</v>
       </c>
       <c r="F15" s="9"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="58">
-        <v>2227015</v>
+      <c r="G15" s="40"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="50">
+        <v>4510299</v>
       </c>
       <c r="K15" s="41"/>
       <c r="L15" s="16"/>
-      <c r="M15" s="55">
-        <v>2054542</v>
-      </c>
-      <c r="N15" s="14"/>
+      <c r="M15" s="46"/>
       <c r="O15" s="26"/>
-      <c r="P15" s="51"/>
-      <c r="Q15" t="s">
-        <v>163</v>
-      </c>
+      <c r="Q15" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="R15" s="12"/>
       <c r="S15" s="27"/>
       <c r="T15" s="29"/>
-      <c r="V15" s="37"/>
+      <c r="U15" s="34">
+        <v>8227</v>
+      </c>
+      <c r="V15" s="38"/>
       <c r="W15" s="32"/>
       <c r="X15" s="31"/>
-      <c r="Y15" s="43">
-        <v>82</v>
-      </c>
-      <c r="AA15" s="45"/>
-      <c r="AB15" s="50"/>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="8">
-        <v>78270</v>
-      </c>
-      <c r="F16" s="9"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="23"/>
-      <c r="I16" s="58">
-        <v>1243724</v>
-      </c>
-      <c r="K16" s="41"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="54"/>
-      <c r="O16" s="26"/>
-      <c r="Q16" t="s">
-        <v>164</v>
-      </c>
-      <c r="R16" s="12"/>
-      <c r="S16" s="27"/>
-      <c r="T16" s="29"/>
-      <c r="U16" s="34">
-        <v>8107</v>
-      </c>
-      <c r="V16" s="38"/>
-      <c r="W16" s="32"/>
-      <c r="X16" s="31"/>
-      <c r="Y16" s="43">
-        <v>125</v>
-      </c>
-      <c r="Z16" s="44"/>
-      <c r="AA16" s="45"/>
-      <c r="AB16" s="50"/>
-    </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+      <c r="D16" s="48"/>
+      <c r="E16" s="54"/>
+      <c r="L16" s="24"/>
+      <c r="M16" s="46"/>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" s="8">
-        <v>78112</v>
-      </c>
-      <c r="F17" s="9"/>
-      <c r="G17" s="40"/>
-      <c r="H17" s="23"/>
-      <c r="I17" s="58">
-        <v>1120625</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="D17" s="48"/>
+      <c r="E17" s="54"/>
       <c r="L17" s="24"/>
-      <c r="M17" s="54"/>
-      <c r="O17" s="26"/>
-      <c r="Q17" t="s">
-        <v>165</v>
-      </c>
-      <c r="R17" s="12"/>
-      <c r="S17" s="27"/>
-      <c r="T17" s="29"/>
-      <c r="U17" s="34">
-        <v>8108</v>
-      </c>
-      <c r="V17" s="38"/>
-      <c r="W17" s="32"/>
-      <c r="X17" s="31"/>
-      <c r="Y17" s="43">
-        <v>141</v>
-      </c>
-      <c r="Z17" s="44"/>
-      <c r="AA17" s="45"/>
-      <c r="AB17" s="50"/>
-    </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="M17" s="46"/>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>24</v>
+        <v>17</v>
+      </c>
+      <c r="D18" s="48"/>
+      <c r="E18" s="54" t="s">
+        <v>18</v>
       </c>
       <c r="F18" s="9"/>
       <c r="G18" s="40"/>
       <c r="H18" s="23"/>
-      <c r="I18" s="58">
-        <v>1735372</v>
+      <c r="I18" s="50">
+        <v>2227007</v>
       </c>
       <c r="K18" s="41"/>
       <c r="L18" s="16"/>
-      <c r="M18" s="55">
-        <v>8072704</v>
+      <c r="M18" s="47">
+        <v>9228446</v>
       </c>
       <c r="N18" s="14"/>
       <c r="O18" s="26"/>
-      <c r="P18" s="51"/>
-      <c r="Q18" t="s">
-        <v>166</v>
+      <c r="P18" s="43"/>
+      <c r="Q18" s="10" t="s">
+        <v>157</v>
       </c>
       <c r="R18" s="12"/>
       <c r="S18" s="27"/>
       <c r="T18" s="29"/>
       <c r="U18" s="34">
-        <v>8448</v>
+        <v>8104</v>
       </c>
       <c r="V18" s="38"/>
       <c r="W18" s="32"/>
       <c r="X18" s="31"/>
-      <c r="Y18" s="43">
-        <v>187</v>
-      </c>
-      <c r="Z18" s="44"/>
-      <c r="AA18" s="45"/>
-      <c r="AB18" s="50"/>
-    </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="I19" s="58">
-        <v>4294294</v>
-      </c>
-      <c r="L19" s="24"/>
-      <c r="M19" s="54"/>
-      <c r="Q19" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="D19" s="48"/>
+      <c r="E19" s="54" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" s="9"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="50">
+        <v>2227015</v>
+      </c>
+      <c r="K19" s="41"/>
+      <c r="L19" s="16"/>
+      <c r="M19" s="47">
+        <v>2054542</v>
+      </c>
+      <c r="N19" s="14"/>
+      <c r="O19" s="26"/>
+      <c r="P19" s="43"/>
+      <c r="Q19" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="S19" s="27"/>
+      <c r="T19" s="29"/>
+      <c r="V19" s="37"/>
+      <c r="W19" s="32"/>
+      <c r="X19" s="31"/>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>25</v>
+        <v>21</v>
+      </c>
+      <c r="E20" s="8">
+        <v>78270</v>
       </c>
       <c r="F20" s="9"/>
       <c r="G20" s="40"/>
       <c r="H20" s="23"/>
-      <c r="I20" s="58">
-        <v>2105773</v>
+      <c r="I20" s="50">
+        <v>1243724</v>
       </c>
       <c r="K20" s="41"/>
       <c r="L20" s="16"/>
-      <c r="M20" s="54"/>
+      <c r="M20" s="46"/>
       <c r="O20" s="26"/>
-      <c r="Q20" t="s">
-        <v>168</v>
-      </c>
+      <c r="Q20" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="R20" s="12"/>
       <c r="S20" s="27"/>
       <c r="T20" s="29"/>
-      <c r="U20" s="34" t="s">
-        <v>26</v>
+      <c r="U20" s="34">
+        <v>8107</v>
       </c>
       <c r="V20" s="38"/>
       <c r="W20" s="32"/>
       <c r="X20" s="31"/>
-      <c r="Y20" s="43">
-        <v>1870</v>
-      </c>
-      <c r="Z20" s="44"/>
-      <c r="AA20" s="45"/>
-      <c r="AB20" s="50"/>
-    </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>27</v>
+        <v>22</v>
+      </c>
+      <c r="E21" s="8">
+        <v>78112</v>
       </c>
       <c r="F21" s="9"/>
       <c r="G21" s="40"/>
       <c r="H21" s="23"/>
-      <c r="I21" s="58">
-        <v>1821537</v>
-      </c>
-      <c r="K21" s="41"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="55">
-        <v>5365192</v>
-      </c>
-      <c r="N21" s="14"/>
+      <c r="I21" s="50">
+        <v>1120625</v>
+      </c>
+      <c r="L21" s="24"/>
+      <c r="M21" s="46"/>
       <c r="O21" s="26"/>
-      <c r="P21" s="51"/>
-      <c r="Q21" t="s">
-        <v>169</v>
-      </c>
+      <c r="Q21" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="R21" s="12"/>
       <c r="S21" s="27"/>
       <c r="T21" s="29"/>
       <c r="U21" s="34">
-        <v>8084</v>
+        <v>8108</v>
       </c>
       <c r="V21" s="38"/>
       <c r="W21" s="32"/>
       <c r="X21" s="31"/>
-      <c r="Y21" s="43">
-        <v>226</v>
-      </c>
-      <c r="Z21" s="44"/>
-      <c r="AA21" s="45"/>
-      <c r="AB21" s="50"/>
-    </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E22" s="8">
-        <v>76346</v>
+        <v>78</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>24</v>
       </c>
       <c r="F22" s="9"/>
       <c r="G22" s="40"/>
       <c r="H22" s="23"/>
-      <c r="I22" s="58">
-        <v>1185545</v>
-      </c>
-      <c r="L22" s="24"/>
-      <c r="M22" s="54"/>
-      <c r="Q22" t="s">
-        <v>170</v>
+      <c r="I22" s="50">
+        <v>1735372</v>
+      </c>
+      <c r="K22" s="41"/>
+      <c r="L22" s="16"/>
+      <c r="M22" s="47">
+        <v>8072704</v>
+      </c>
+      <c r="N22" s="14"/>
+      <c r="O22" s="26"/>
+      <c r="P22" s="43"/>
+      <c r="Q22" s="10" t="s">
+        <v>161</v>
       </c>
       <c r="R22" s="12"/>
       <c r="S22" s="27"/>
       <c r="T22" s="29"/>
       <c r="U22" s="34">
-        <v>8153</v>
+        <v>8448</v>
       </c>
       <c r="V22" s="38"/>
       <c r="W22" s="32"/>
       <c r="X22" s="31"/>
-      <c r="Y22" s="43">
-        <v>237</v>
-      </c>
-      <c r="Z22" s="44"/>
-      <c r="AA22" s="45"/>
-      <c r="AB22" s="50"/>
-    </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="I23" s="58" t="s">
-        <v>143</v>
+        <v>131</v>
+      </c>
+      <c r="I23" s="50">
+        <v>4294294</v>
       </c>
       <c r="L23" s="24"/>
-      <c r="M23" s="54">
-        <v>4056479</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="M23" s="46"/>
+      <c r="Q23" s="10" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E24" s="8">
-        <v>78922</v>
+        <v>79</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="F24" s="9"/>
       <c r="G24" s="40"/>
       <c r="H24" s="23"/>
-      <c r="I24" s="58" t="s">
-        <v>142</v>
-      </c>
-      <c r="L24" s="24"/>
-      <c r="M24" s="55"/>
-      <c r="N24" s="14"/>
+      <c r="I24" s="50">
+        <v>2105773</v>
+      </c>
+      <c r="K24" s="41"/>
+      <c r="L24" s="16"/>
+      <c r="M24" s="46"/>
       <c r="O24" s="26"/>
-      <c r="P24" s="51"/>
-      <c r="Q24" t="s">
-        <v>172</v>
-      </c>
-      <c r="R24" s="12"/>
+      <c r="Q24" s="10" t="s">
+        <v>163</v>
+      </c>
       <c r="S24" s="27"/>
       <c r="T24" s="29"/>
-      <c r="U24" s="34">
-        <v>4094</v>
+      <c r="U24" s="34" t="s">
+        <v>26</v>
       </c>
       <c r="V24" s="38"/>
       <c r="W24" s="32"/>
       <c r="X24" s="31"/>
-      <c r="Y24" s="43">
-        <v>1250</v>
-      </c>
-      <c r="Z24" s="44"/>
-      <c r="AA24" s="45"/>
-      <c r="AB24" s="50"/>
-    </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E25" s="8"/>
-      <c r="H25" s="22"/>
-      <c r="I25" s="58" t="s">
-        <v>144</v>
-      </c>
-      <c r="L25" s="24"/>
-      <c r="M25" s="54"/>
-      <c r="Q25" t="s">
-        <v>173</v>
+        <v>80</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F25" s="9"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="50">
+        <v>1821537</v>
+      </c>
+      <c r="K25" s="41"/>
+      <c r="L25" s="16"/>
+      <c r="M25" s="47">
+        <v>5365192</v>
+      </c>
+      <c r="N25" s="14"/>
+      <c r="O25" s="26"/>
+      <c r="P25" s="43"/>
+      <c r="Q25" s="10" t="s">
+        <v>164</v>
       </c>
       <c r="S25" s="27"/>
       <c r="T25" s="29"/>
-      <c r="V25" s="37"/>
+      <c r="U25" s="34">
+        <v>8084</v>
+      </c>
+      <c r="V25" s="38"/>
       <c r="W25" s="32"/>
       <c r="X25" s="31"/>
-      <c r="Y25" s="43">
-        <v>15</v>
-      </c>
-      <c r="AA25" s="45"/>
-      <c r="AB25" s="50"/>
-    </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E26" s="8">
-        <v>74968</v>
+        <v>76346</v>
       </c>
       <c r="F26" s="9"/>
       <c r="G26" s="40"/>
       <c r="H26" s="23"/>
-      <c r="I26" s="58">
-        <v>1810910</v>
-      </c>
-      <c r="K26" s="41"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="54"/>
-      <c r="Q26" t="s">
-        <v>174</v>
+      <c r="I26" s="50">
+        <v>1185545</v>
+      </c>
+      <c r="L26" s="24"/>
+      <c r="M26" s="46"/>
+      <c r="Q26" s="10" t="s">
+        <v>165</v>
       </c>
       <c r="R26" s="12"/>
       <c r="S26" s="27"/>
       <c r="T26" s="29"/>
       <c r="U26" s="34">
-        <v>8076</v>
+        <v>8153</v>
       </c>
       <c r="V26" s="38"/>
       <c r="W26" s="32"/>
       <c r="X26" s="31"/>
-      <c r="Y26" s="43">
-        <v>14</v>
-      </c>
-      <c r="Z26" s="44"/>
-      <c r="AA26" s="45"/>
-      <c r="AB26" s="50"/>
-    </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" s="9"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="23"/>
-      <c r="I27" s="58">
-        <v>7975374</v>
-      </c>
-      <c r="K27" s="41"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="55">
-        <v>9546982</v>
-      </c>
-      <c r="N27" s="14"/>
-      <c r="O27" s="26"/>
-      <c r="P27" s="51"/>
-      <c r="Q27" t="s">
-        <v>175</v>
-      </c>
-      <c r="S27" s="27"/>
-      <c r="T27" s="29"/>
-      <c r="U27" s="34">
-        <v>8279</v>
-      </c>
-      <c r="V27" s="38"/>
-      <c r="W27" s="32"/>
-      <c r="X27" s="31"/>
-      <c r="Y27" s="43">
-        <v>386</v>
-      </c>
-      <c r="Z27" s="44"/>
-      <c r="AA27" s="45"/>
-      <c r="AB27" s="50"/>
-    </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+      <c r="I27" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="L27" s="24"/>
+      <c r="M27" s="46">
+        <v>4056479</v>
+      </c>
+      <c r="Q27" s="10" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="I28" s="58" t="s">
-        <v>145</v>
+        <v>81</v>
+      </c>
+      <c r="E28" s="8">
+        <v>78922</v>
+      </c>
+      <c r="F28" s="9"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="50" t="s">
+        <v>137</v>
       </c>
       <c r="L28" s="24"/>
-      <c r="M28" s="54"/>
-      <c r="Q28" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="M28" s="47"/>
+      <c r="N28" s="14"/>
+      <c r="O28" s="26"/>
+      <c r="P28" s="43"/>
+      <c r="Q28" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="R28" s="12"/>
+      <c r="S28" s="27"/>
+      <c r="T28" s="29"/>
+      <c r="U28" s="34">
+        <v>4094</v>
+      </c>
+      <c r="V28" s="38"/>
+      <c r="W28" s="32"/>
+      <c r="X28" s="31"/>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E29" s="8"/>
+        <v>29</v>
+      </c>
       <c r="H29" s="22"/>
-      <c r="I29" s="58" t="s">
-        <v>146</v>
+      <c r="I29" s="50" t="s">
+        <v>139</v>
       </c>
       <c r="L29" s="24"/>
-      <c r="M29" s="54"/>
-      <c r="Q29" t="s">
-        <v>177</v>
+      <c r="M29" s="46"/>
+      <c r="Q29" s="10" t="s">
+        <v>168</v>
       </c>
       <c r="S29" s="27"/>
       <c r="T29" s="29"/>
-      <c r="U29" s="34">
-        <v>8324</v>
-      </c>
-      <c r="V29" s="38"/>
+      <c r="V29" s="37"/>
       <c r="W29" s="32"/>
       <c r="X29" s="31"/>
-      <c r="Y29" s="43">
-        <v>60</v>
-      </c>
-      <c r="Z29" s="44"/>
-      <c r="AA29" s="45"/>
-      <c r="AB29" s="50"/>
-    </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>16</v>
+        <v>30</v>
+      </c>
+      <c r="E30" s="8">
+        <v>74968</v>
       </c>
       <c r="F30" s="9"/>
       <c r="G30" s="40"/>
       <c r="H30" s="23"/>
-      <c r="I30">
-        <v>7779911</v>
+      <c r="I30" s="50">
+        <v>1810910</v>
       </c>
       <c r="K30" s="41"/>
       <c r="L30" s="16"/>
-      <c r="M30" s="59">
-        <v>3332830</v>
-      </c>
-      <c r="N30" s="14"/>
-      <c r="O30" s="26"/>
-      <c r="P30" s="52"/>
-      <c r="Q30" t="s">
-        <v>178</v>
+      <c r="M30" s="46"/>
+      <c r="Q30" s="10" t="s">
+        <v>169</v>
       </c>
       <c r="R30" s="12"/>
       <c r="S30" s="27"/>
       <c r="T30" s="29"/>
       <c r="U30" s="34">
-        <v>8612</v>
+        <v>8076</v>
       </c>
       <c r="V30" s="38"/>
       <c r="W30" s="32"/>
       <c r="X30" s="31"/>
-      <c r="Y30" s="43">
-        <v>170</v>
-      </c>
-      <c r="Z30" s="44"/>
-      <c r="AA30" s="45"/>
-      <c r="AB30" s="50"/>
-    </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E31" s="8">
-        <v>77264</v>
+        <v>73</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>10</v>
       </c>
       <c r="F31" s="9"/>
       <c r="G31" s="40"/>
       <c r="H31" s="23"/>
-      <c r="I31" s="58">
-        <v>2260149</v>
+      <c r="I31" s="50">
+        <v>7975374</v>
       </c>
       <c r="K31" s="41"/>
       <c r="L31" s="16"/>
-      <c r="M31" s="54"/>
-      <c r="Q31" t="s">
-        <v>179</v>
-      </c>
-      <c r="R31" s="12"/>
+      <c r="M31" s="47">
+        <v>9546982</v>
+      </c>
+      <c r="N31" s="14"/>
+      <c r="O31" s="26"/>
+      <c r="P31" s="43"/>
+      <c r="Q31" s="10" t="s">
+        <v>170</v>
+      </c>
       <c r="S31" s="27"/>
       <c r="T31" s="29"/>
       <c r="U31" s="34">
-        <v>8236</v>
+        <v>8279</v>
       </c>
       <c r="V31" s="38"/>
       <c r="W31" s="32"/>
       <c r="X31" s="31"/>
-      <c r="Y31" s="43">
-        <v>176</v>
-      </c>
-      <c r="Z31" s="44"/>
-      <c r="AA31" s="45"/>
-      <c r="AB31" s="50"/>
-    </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F32" s="9"/>
-      <c r="G32" s="40"/>
-      <c r="H32" s="23"/>
-      <c r="I32" s="58">
-        <v>1723857</v>
-      </c>
-      <c r="K32" s="41"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="55"/>
-      <c r="N32" s="14"/>
-      <c r="O32" s="26"/>
-      <c r="P32" s="51"/>
-      <c r="Q32" t="s">
-        <v>180</v>
-      </c>
-      <c r="S32" s="27"/>
-      <c r="T32" s="29"/>
-      <c r="U32" s="34" t="s">
-        <v>64</v>
-      </c>
-      <c r="V32" s="37"/>
-      <c r="W32" s="32"/>
-      <c r="X32" s="31"/>
-      <c r="Y32" s="43">
-        <v>321</v>
-      </c>
-      <c r="AA32" s="45"/>
-      <c r="AB32" s="50"/>
-    </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+      <c r="I32" s="50" t="s">
+        <v>140</v>
+      </c>
+      <c r="L32" s="24"/>
+      <c r="M32" s="46"/>
+      <c r="Q32" s="10" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F33" s="9"/>
-      <c r="G33" s="40"/>
-      <c r="H33" s="23"/>
-      <c r="I33" s="58">
-        <v>7199706</v>
-      </c>
-      <c r="K33" s="41"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="59">
-        <v>3355294</v>
-      </c>
-      <c r="N33" s="14"/>
-      <c r="O33" s="26"/>
-      <c r="P33" s="51"/>
-      <c r="Q33"/>
-      <c r="R33" s="12"/>
+        <v>75</v>
+      </c>
+      <c r="H33" s="22"/>
+      <c r="I33" s="50" t="s">
+        <v>141</v>
+      </c>
+      <c r="L33" s="24"/>
+      <c r="M33" s="46"/>
+      <c r="Q33" s="10" t="s">
+        <v>172</v>
+      </c>
       <c r="S33" s="27"/>
       <c r="T33" s="29"/>
+      <c r="U33" s="34">
+        <v>8324</v>
+      </c>
       <c r="V33" s="38"/>
       <c r="W33" s="32"/>
       <c r="X33" s="31"/>
-      <c r="Z33" s="44"/>
-      <c r="AA33" s="45"/>
-      <c r="AB33" s="50"/>
-    </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E34" s="8"/>
-      <c r="H34" s="22"/>
-      <c r="I34" s="58">
-        <v>1008143</v>
+        <v>76</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F34" s="9"/>
+      <c r="G34" s="40"/>
+      <c r="H34" s="23"/>
+      <c r="I34" s="50">
+        <v>7779911</v>
       </c>
       <c r="K34" s="41"/>
       <c r="L34" s="16"/>
-      <c r="M34" s="54"/>
-      <c r="Q34" t="s">
-        <v>181</v>
-      </c>
+      <c r="M34" s="53">
+        <v>3332830</v>
+      </c>
+      <c r="N34" s="14"/>
+      <c r="O34" s="26"/>
+      <c r="P34" s="44"/>
+      <c r="Q34" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="R34" s="12"/>
       <c r="S34" s="27"/>
       <c r="T34" s="29"/>
       <c r="U34" s="34">
-        <v>8238</v>
+        <v>8612</v>
       </c>
       <c r="V34" s="38"/>
       <c r="W34" s="32"/>
       <c r="X34" s="31"/>
-      <c r="Y34" s="43">
-        <v>275</v>
-      </c>
-      <c r="Z34" s="44"/>
-      <c r="AA34" s="45"/>
-      <c r="AB34" s="50"/>
-    </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E35" s="8"/>
-      <c r="H35" s="22"/>
-      <c r="I35" s="58">
-        <v>1985274</v>
+        <v>77</v>
+      </c>
+      <c r="E35" s="8">
+        <v>77264</v>
+      </c>
+      <c r="F35" s="9"/>
+      <c r="G35" s="40"/>
+      <c r="H35" s="23"/>
+      <c r="I35" s="50">
+        <v>2260149</v>
       </c>
       <c r="K35" s="41"/>
       <c r="L35" s="16"/>
-      <c r="M35" s="59">
-        <v>9046103</v>
-      </c>
-      <c r="N35" s="14"/>
-      <c r="O35" s="26"/>
-      <c r="P35" s="51"/>
-      <c r="Q35" t="s">
-        <v>182</v>
+      <c r="M35" s="46"/>
+      <c r="Q35" s="10" t="s">
+        <v>174</v>
       </c>
       <c r="R35" s="12"/>
       <c r="S35" s="27"/>
       <c r="T35" s="29"/>
+      <c r="U35" s="34">
+        <v>8236</v>
+      </c>
       <c r="V35" s="38"/>
       <c r="W35" s="32"/>
       <c r="X35" s="31"/>
-      <c r="Z35" s="44"/>
-      <c r="AA35" s="45"/>
-      <c r="AB35" s="50"/>
-    </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="I36" s="58" t="s">
-        <v>147</v>
-      </c>
-      <c r="L36" s="24"/>
-      <c r="M36" s="54"/>
-      <c r="Q36" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F36" s="9"/>
+      <c r="G36" s="40"/>
+      <c r="H36" s="23"/>
+      <c r="I36" s="50">
+        <v>1723857</v>
+      </c>
+      <c r="K36" s="41"/>
+      <c r="L36" s="16"/>
+      <c r="M36" s="47"/>
+      <c r="N36" s="14"/>
+      <c r="O36" s="26"/>
+      <c r="P36" s="43"/>
+      <c r="Q36" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="S36" s="27"/>
+      <c r="T36" s="29"/>
+      <c r="U36" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="V36" s="37"/>
+      <c r="W36" s="32"/>
+      <c r="X36" s="31"/>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="F37" s="9"/>
       <c r="G37" s="40"/>
       <c r="H37" s="23"/>
-      <c r="I37" s="58">
-        <v>2416691</v>
+      <c r="I37" s="50">
+        <v>7199706</v>
       </c>
       <c r="K37" s="41"/>
       <c r="L37" s="16"/>
-      <c r="M37" s="55">
-        <v>7217979</v>
+      <c r="M37" s="53">
+        <v>3355294</v>
       </c>
       <c r="N37" s="14"/>
       <c r="O37" s="26"/>
-      <c r="P37" s="51"/>
-      <c r="Q37" t="s">
-        <v>184</v>
-      </c>
+      <c r="P37" s="43"/>
       <c r="R37" s="12"/>
       <c r="S37" s="27"/>
       <c r="T37" s="29"/>
-      <c r="U37" s="34">
-        <v>8380</v>
-      </c>
       <c r="V37" s="38"/>
       <c r="W37" s="32"/>
       <c r="X37" s="31"/>
-      <c r="Y37" s="43">
-        <v>340</v>
-      </c>
-      <c r="Z37" s="44"/>
-      <c r="AA37" s="45"/>
-      <c r="AB37" s="50"/>
-    </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F38" s="9"/>
-      <c r="G38" s="40"/>
-      <c r="H38" s="23"/>
-      <c r="L38" s="24"/>
-      <c r="M38" s="54"/>
-      <c r="Q38" t="s">
-        <v>185</v>
+        <v>83</v>
+      </c>
+      <c r="H38" s="22"/>
+      <c r="I38" s="50">
+        <v>1008143</v>
+      </c>
+      <c r="K38" s="41"/>
+      <c r="L38" s="16"/>
+      <c r="M38" s="46"/>
+      <c r="Q38" s="10" t="s">
+        <v>176</v>
       </c>
       <c r="S38" s="27"/>
       <c r="T38" s="29"/>
-      <c r="V38" s="37"/>
+      <c r="U38" s="34">
+        <v>8238</v>
+      </c>
+      <c r="V38" s="38"/>
       <c r="W38" s="32"/>
       <c r="X38" s="31"/>
-      <c r="Y38" s="43">
-        <v>347</v>
-      </c>
-      <c r="AA38" s="45"/>
-      <c r="AB38" s="50"/>
-    </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E39" s="8">
-        <v>93004</v>
-      </c>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
+        <v>84</v>
+      </c>
       <c r="H39" s="22"/>
-      <c r="L39" s="24"/>
-      <c r="M39" s="54"/>
-      <c r="Q39" t="s">
-        <v>186</v>
-      </c>
+      <c r="I39" s="50">
+        <v>1985274</v>
+      </c>
+      <c r="K39" s="41"/>
+      <c r="L39" s="16"/>
+      <c r="M39" s="53">
+        <v>9046103</v>
+      </c>
+      <c r="N39" s="14"/>
+      <c r="O39" s="26"/>
+      <c r="P39" s="43"/>
+      <c r="Q39" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="R39" s="12"/>
       <c r="S39" s="27"/>
       <c r="T39" s="29"/>
-      <c r="V39" s="37"/>
+      <c r="V39" s="38"/>
       <c r="W39" s="32"/>
       <c r="X39" s="31"/>
-      <c r="Y39" s="43">
-        <v>385</v>
-      </c>
-      <c r="AA39" s="45"/>
-      <c r="AB39" s="50"/>
-    </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F40" s="9"/>
-      <c r="G40" s="40"/>
-      <c r="H40" s="23"/>
-      <c r="I40" s="58">
-        <v>8474538</v>
-      </c>
-      <c r="K40" s="41"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="59">
-        <v>4425690</v>
-      </c>
-      <c r="N40" s="14"/>
-      <c r="O40" s="26"/>
-      <c r="P40" s="51"/>
-      <c r="Q40" t="s">
-        <v>187</v>
-      </c>
-      <c r="R40" s="12"/>
-      <c r="S40" s="27"/>
-      <c r="T40" s="29"/>
-      <c r="U40" s="34">
-        <v>8209</v>
-      </c>
-      <c r="V40" s="38"/>
-      <c r="W40" s="32"/>
-      <c r="X40" s="31"/>
-      <c r="Y40" s="43">
-        <v>833</v>
-      </c>
-      <c r="Z40" s="44"/>
-      <c r="AA40" s="45"/>
-      <c r="AB40" s="50"/>
-    </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="I40" s="50" t="s">
+        <v>142</v>
+      </c>
+      <c r="L40" s="24"/>
+      <c r="M40" s="46"/>
+      <c r="Q40" s="10" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F41" s="9"/>
       <c r="G41" s="40"/>
       <c r="H41" s="23"/>
-      <c r="I41" s="58">
-        <v>3629433</v>
+      <c r="I41" s="50">
+        <v>2416691</v>
       </c>
       <c r="K41" s="41"/>
       <c r="L41" s="16"/>
-      <c r="M41" s="59">
-        <v>2326445</v>
-      </c>
+      <c r="M41" s="47">
+        <v>7217979</v>
+      </c>
+      <c r="N41" s="14"/>
       <c r="O41" s="26"/>
-      <c r="Q41" t="s">
-        <v>186</v>
-      </c>
+      <c r="P41" s="43"/>
+      <c r="Q41" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="R41" s="12"/>
       <c r="S41" s="27"/>
       <c r="T41" s="29"/>
       <c r="U41" s="34">
-        <v>8520</v>
+        <v>8380</v>
       </c>
       <c r="V41" s="38"/>
       <c r="W41" s="32"/>
       <c r="X41" s="31"/>
-      <c r="Z41" s="44"/>
-      <c r="AA41" s="45"/>
-      <c r="AB41" s="50"/>
-    </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F42" s="9"/>
       <c r="G42" s="40"/>
       <c r="H42" s="23"/>
       <c r="L42" s="24"/>
-      <c r="M42" s="54"/>
-      <c r="Q42" t="s">
-        <v>188</v>
-      </c>
-      <c r="R42" s="12"/>
+      <c r="M42" s="46"/>
+      <c r="Q42" s="10" t="s">
+        <v>180</v>
+      </c>
       <c r="S42" s="27"/>
       <c r="T42" s="29"/>
-      <c r="U42" s="34">
-        <v>8297</v>
-      </c>
-      <c r="V42" s="38"/>
+      <c r="V42" s="37"/>
       <c r="W42" s="32"/>
       <c r="X42" s="31"/>
-      <c r="Z42" s="44"/>
-      <c r="AA42" s="45"/>
-      <c r="AB42" s="50"/>
-    </row>
-    <row r="43" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>23</v>
+        <v>106</v>
+      </c>
+      <c r="E43" s="8">
+        <v>93004</v>
       </c>
       <c r="F43" s="9"/>
-      <c r="G43" s="40"/>
-      <c r="H43" s="23"/>
-      <c r="I43" s="58" t="s">
-        <v>148</v>
-      </c>
+      <c r="G43" s="9"/>
+      <c r="H43" s="22"/>
       <c r="L43" s="24"/>
-      <c r="M43" s="59">
-        <v>6579288</v>
-      </c>
-      <c r="N43" s="14"/>
-      <c r="O43" s="26"/>
-      <c r="P43" s="51"/>
-      <c r="Q43" t="s">
-        <v>189</v>
-      </c>
-      <c r="R43" s="12"/>
+      <c r="M43" s="46"/>
+      <c r="Q43" s="10" t="s">
+        <v>181</v>
+      </c>
       <c r="S43" s="27"/>
       <c r="T43" s="29"/>
-      <c r="U43" s="34">
-        <v>8052</v>
-      </c>
-      <c r="V43" s="38"/>
+      <c r="V43" s="37"/>
       <c r="W43" s="32"/>
       <c r="X43" s="31"/>
-      <c r="Y43" s="43">
-        <v>253</v>
-      </c>
-      <c r="Z43" s="44"/>
-      <c r="AA43" s="45"/>
-      <c r="AB43" s="50"/>
-    </row>
-    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E44" s="8">
-        <v>75778</v>
+        <v>107</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>56</v>
       </c>
       <c r="F44" s="9"/>
       <c r="G44" s="40"/>
       <c r="H44" s="23"/>
-      <c r="I44" s="58">
-        <v>2005346</v>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="53"/>
-      <c r="M44" s="54"/>
-      <c r="Q44" t="s">
-        <v>190</v>
+      <c r="I44" s="50">
+        <v>8474538</v>
+      </c>
+      <c r="K44" s="41"/>
+      <c r="L44" s="16"/>
+      <c r="M44" s="53">
+        <v>4425690</v>
+      </c>
+      <c r="N44" s="14"/>
+      <c r="O44" s="26"/>
+      <c r="P44" s="43"/>
+      <c r="Q44" s="10" t="s">
+        <v>182</v>
       </c>
       <c r="R44" s="12"/>
       <c r="S44" s="27"/>
       <c r="T44" s="29"/>
       <c r="U44" s="34">
-        <v>8178</v>
+        <v>8209</v>
       </c>
       <c r="V44" s="38"/>
       <c r="W44" s="32"/>
       <c r="X44" s="31"/>
-      <c r="Y44" s="43">
-        <v>259</v>
-      </c>
-      <c r="Z44" s="44"/>
-      <c r="AA44" s="45"/>
-      <c r="AB44" s="50"/>
-    </row>
-    <row r="45" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="F45" s="9"/>
       <c r="G45" s="40"/>
       <c r="H45" s="23"/>
-      <c r="I45" s="58" t="s">
-        <v>149</v>
-      </c>
-      <c r="L45" s="24"/>
-      <c r="M45" s="59">
-        <v>6114656</v>
-      </c>
-      <c r="N45" s="14"/>
+      <c r="I45" s="50">
+        <v>3629433</v>
+      </c>
+      <c r="K45" s="41"/>
+      <c r="L45" s="16"/>
+      <c r="M45" s="53">
+        <v>2326445</v>
+      </c>
       <c r="O45" s="26"/>
-      <c r="P45" s="51"/>
-      <c r="Q45" t="s">
-        <v>191</v>
-      </c>
-      <c r="R45" s="12"/>
+      <c r="Q45" s="10" t="s">
+        <v>181</v>
+      </c>
       <c r="S45" s="27"/>
       <c r="T45" s="29"/>
       <c r="U45" s="34">
-        <v>8133</v>
+        <v>8520</v>
       </c>
       <c r="V45" s="38"/>
       <c r="W45" s="32"/>
       <c r="X45" s="31"/>
-      <c r="Y45" s="43">
-        <v>554</v>
-      </c>
-      <c r="Z45" s="44"/>
-      <c r="AA45" s="45"/>
-      <c r="AB45" s="50"/>
-    </row>
-    <row r="46" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="F46" s="9"/>
       <c r="G46" s="40"/>
       <c r="H46" s="23"/>
-      <c r="I46" s="58">
-        <v>2219111</v>
-      </c>
-      <c r="K46" s="41"/>
-      <c r="L46" s="16"/>
-      <c r="Q46" t="s">
-        <v>192</v>
-      </c>
+      <c r="L46" s="24"/>
+      <c r="M46" s="46"/>
+      <c r="Q46" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="R46" s="12"/>
       <c r="S46" s="27"/>
       <c r="T46" s="29"/>
-      <c r="V46" s="37"/>
+      <c r="U46" s="34">
+        <v>8297</v>
+      </c>
+      <c r="V46" s="38"/>
       <c r="W46" s="32"/>
       <c r="X46" s="31"/>
-      <c r="Y46" s="43">
-        <v>556</v>
-      </c>
-      <c r="AA46" s="45"/>
-      <c r="AB46" s="50"/>
-    </row>
-    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>74</v>
+        <v>117</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F47" s="9"/>
-      <c r="G47" s="9"/>
-      <c r="H47" s="22"/>
-      <c r="I47" s="58">
-        <v>2004547</v>
-      </c>
-      <c r="K47" s="41"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="54"/>
+      <c r="G47" s="40"/>
+      <c r="H47" s="23"/>
+      <c r="I47" s="50" t="s">
+        <v>143</v>
+      </c>
+      <c r="L47" s="24"/>
+      <c r="M47" s="53">
+        <v>6579288</v>
+      </c>
+      <c r="N47" s="14"/>
       <c r="O47" s="26"/>
-      <c r="Q47" t="s">
-        <v>193</v>
+      <c r="P47" s="43"/>
+      <c r="Q47" s="10" t="s">
+        <v>184</v>
       </c>
       <c r="R47" s="12"/>
       <c r="S47" s="27"/>
       <c r="T47" s="29"/>
       <c r="U47" s="34">
-        <v>8170</v>
+        <v>8052</v>
       </c>
       <c r="V47" s="38"/>
       <c r="W47" s="32"/>
       <c r="X47" s="31"/>
-      <c r="Y47" s="43">
-        <v>251</v>
-      </c>
-      <c r="Z47" s="44"/>
-      <c r="AA47" s="45"/>
-      <c r="AB47" s="50"/>
-    </row>
-    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>31</v>
+        <v>93</v>
       </c>
       <c r="E48" s="8">
-        <v>77662</v>
+        <v>75778</v>
       </c>
       <c r="F48" s="9"/>
       <c r="G48" s="40"/>
       <c r="H48" s="23"/>
-      <c r="I48" s="58">
-        <v>1290469</v>
-      </c>
-      <c r="K48" s="41"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="54"/>
-      <c r="Q48" t="s">
-        <v>194</v>
+      <c r="I48" s="50">
+        <v>2005346</v>
+      </c>
+      <c r="K48" s="16"/>
+      <c r="L48" s="45"/>
+      <c r="M48" s="46"/>
+      <c r="Q48" s="10" t="s">
+        <v>185</v>
       </c>
       <c r="R48" s="12"/>
       <c r="S48" s="27"/>
       <c r="T48" s="29"/>
       <c r="U48" s="34">
-        <v>4185</v>
+        <v>8178</v>
       </c>
       <c r="V48" s="38"/>
       <c r="W48" s="32"/>
       <c r="X48" s="31"/>
-      <c r="Y48" s="43">
-        <v>1305</v>
-      </c>
-      <c r="Z48" s="44"/>
-      <c r="AA48" s="45"/>
-      <c r="AB48" s="50"/>
-    </row>
-    <row r="49" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E49" s="8"/>
+        <v>94</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>44</v>
+      </c>
       <c r="F49" s="9"/>
       <c r="G49" s="40"/>
       <c r="H49" s="23"/>
-      <c r="I49" s="58">
-        <v>1008168</v>
-      </c>
-      <c r="K49" s="41"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="54"/>
+      <c r="I49" s="50" t="s">
+        <v>144</v>
+      </c>
+      <c r="L49" s="24"/>
+      <c r="M49" s="53">
+        <v>6114656</v>
+      </c>
+      <c r="N49" s="14"/>
       <c r="O49" s="26"/>
-      <c r="Q49" t="s">
-        <v>195</v>
+      <c r="P49" s="43"/>
+      <c r="Q49" s="10" t="s">
+        <v>186</v>
       </c>
       <c r="R49" s="12"/>
       <c r="S49" s="27"/>
       <c r="T49" s="29"/>
       <c r="U49" s="34">
-        <v>8122</v>
+        <v>8133</v>
       </c>
       <c r="V49" s="38"/>
       <c r="W49" s="32"/>
       <c r="X49" s="31"/>
-      <c r="Y49" s="43">
-        <v>285</v>
-      </c>
-      <c r="Z49" s="44"/>
-      <c r="AA49" s="45"/>
-      <c r="AB49" s="50"/>
-    </row>
-    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E50" s="8">
-        <v>78294</v>
+        <v>95</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>45</v>
       </c>
       <c r="F50" s="9"/>
       <c r="G50" s="40"/>
       <c r="H50" s="23"/>
-      <c r="I50" s="58">
-        <v>2252039</v>
+      <c r="I50" s="50">
+        <v>2219111</v>
       </c>
       <c r="K50" s="41"/>
       <c r="L50" s="16"/>
-      <c r="M50" s="56">
-        <v>5384284</v>
-      </c>
-      <c r="O50" s="26"/>
-      <c r="Q50" t="s">
-        <v>196</v>
-      </c>
-      <c r="R50" s="12"/>
+      <c r="M50" s="46"/>
+      <c r="Q50" s="10" t="s">
+        <v>187</v>
+      </c>
       <c r="S50" s="27"/>
       <c r="T50" s="29"/>
-      <c r="U50" s="34">
-        <v>4186</v>
-      </c>
-      <c r="V50" s="38"/>
+      <c r="V50" s="37"/>
       <c r="W50" s="32"/>
       <c r="X50" s="31"/>
-      <c r="Y50" s="43">
-        <v>1330</v>
-      </c>
-      <c r="Z50" s="44"/>
-      <c r="AA50" s="45"/>
-      <c r="AB50" s="50"/>
-    </row>
-    <row r="51" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E51" s="8">
-        <v>16146</v>
+        <v>74</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>12</v>
       </c>
       <c r="F51" s="9"/>
-      <c r="G51" s="40"/>
-      <c r="H51" s="23"/>
-      <c r="I51" s="58">
-        <v>1079425</v>
+      <c r="G51" s="9"/>
+      <c r="H51" s="22"/>
+      <c r="I51" s="50">
+        <v>2004547</v>
       </c>
       <c r="K51" s="41"/>
       <c r="L51" s="16"/>
-      <c r="M51" s="56">
-        <v>3114824</v>
-      </c>
-      <c r="N51" s="14"/>
+      <c r="M51" s="46"/>
       <c r="O51" s="26"/>
-      <c r="P51" s="51"/>
-      <c r="Q51" t="s">
-        <v>197</v>
+      <c r="Q51" s="10" t="s">
+        <v>188</v>
       </c>
       <c r="R51" s="12"/>
       <c r="S51" s="27"/>
       <c r="T51" s="29"/>
-      <c r="U51" s="34" t="s">
-        <v>37</v>
+      <c r="U51" s="34">
+        <v>8170</v>
       </c>
       <c r="V51" s="38"/>
       <c r="W51" s="32"/>
       <c r="X51" s="31"/>
-      <c r="Y51" s="43">
-        <v>1350</v>
-      </c>
-      <c r="Z51" s="44"/>
-      <c r="AA51" s="45"/>
-      <c r="AB51" s="50"/>
-    </row>
-    <row r="52" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="I52" s="56">
-        <v>2030393</v>
-      </c>
-      <c r="L52" s="24"/>
-      <c r="M52" s="54"/>
-      <c r="Q52" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="E52" s="8">
+        <v>77662</v>
+      </c>
+      <c r="F52" s="9"/>
+      <c r="G52" s="40"/>
+      <c r="H52" s="23"/>
+      <c r="I52" s="50">
+        <v>1290469</v>
+      </c>
+      <c r="K52" s="41"/>
+      <c r="L52" s="16"/>
+      <c r="M52" s="46"/>
+      <c r="Q52" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="R52" s="12"/>
+      <c r="S52" s="27"/>
+      <c r="T52" s="29"/>
+      <c r="U52" s="34">
+        <v>4185</v>
+      </c>
+      <c r="V52" s="38"/>
+      <c r="W52" s="32"/>
+      <c r="X52" s="31"/>
+    </row>
+    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E53" s="8">
-        <v>75104</v>
+        <v>32</v>
       </c>
       <c r="F53" s="9"/>
       <c r="G53" s="40"/>
       <c r="H53" s="23"/>
-      <c r="I53" s="58">
-        <v>1164375</v>
+      <c r="I53" s="50">
+        <v>1008168</v>
       </c>
       <c r="K53" s="41"/>
-      <c r="L53" s="24"/>
-      <c r="M53" s="54"/>
-      <c r="Q53" t="s">
-        <v>199</v>
+      <c r="L53" s="16"/>
+      <c r="M53" s="46"/>
+      <c r="O53" s="26"/>
+      <c r="Q53" s="10" t="s">
+        <v>190</v>
       </c>
       <c r="R53" s="12"/>
       <c r="S53" s="27"/>
       <c r="T53" s="29"/>
       <c r="U53" s="34">
-        <v>4176</v>
+        <v>8122</v>
       </c>
       <c r="V53" s="38"/>
       <c r="W53" s="32"/>
       <c r="X53" s="31"/>
-      <c r="Y53" s="43">
-        <v>1375</v>
-      </c>
-      <c r="Z53" s="44"/>
-      <c r="AA53" s="45"/>
-      <c r="AB53" s="50"/>
-    </row>
-    <row r="54" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>82</v>
+        <v>33</v>
       </c>
       <c r="E54" s="8">
-        <v>75736</v>
+        <v>78294</v>
       </c>
       <c r="F54" s="9"/>
       <c r="G54" s="40"/>
       <c r="H54" s="23"/>
-      <c r="I54" s="58">
-        <v>1354135</v>
+      <c r="I54" s="50">
+        <v>2252039</v>
       </c>
       <c r="K54" s="41"/>
       <c r="L54" s="16"/>
-      <c r="M54" s="62">
-        <v>1457100</v>
-      </c>
-      <c r="N54" s="14"/>
+      <c r="M54" s="46">
+        <v>5384284</v>
+      </c>
       <c r="O54" s="26"/>
-      <c r="P54" s="51"/>
-      <c r="Q54" t="s">
-        <v>200</v>
+      <c r="Q54" s="10" t="s">
+        <v>191</v>
       </c>
       <c r="R54" s="12"/>
       <c r="S54" s="27"/>
       <c r="T54" s="29"/>
       <c r="U54" s="34">
-        <v>4184</v>
+        <v>4186</v>
       </c>
       <c r="V54" s="38"/>
       <c r="W54" s="32"/>
       <c r="X54" s="31"/>
-      <c r="Y54" s="43">
-        <v>1425</v>
-      </c>
-      <c r="Z54" s="44"/>
-      <c r="AA54" s="45"/>
-      <c r="AB54" s="50"/>
-    </row>
-    <row r="55" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>114</v>
+        <v>36</v>
       </c>
       <c r="E55" s="8">
-        <v>74844</v>
+        <v>16146</v>
       </c>
       <c r="F55" s="9"/>
       <c r="G55" s="40"/>
       <c r="H55" s="23"/>
-      <c r="I55" s="58">
-        <v>9173196</v>
+      <c r="I55" s="50">
+        <v>1079425</v>
       </c>
       <c r="K55" s="41"/>
-      <c r="L55" s="24"/>
-      <c r="M55" s="61">
-        <v>2016442</v>
+      <c r="L55" s="16"/>
+      <c r="M55" s="46">
+        <v>3114824</v>
       </c>
       <c r="N55" s="14"/>
       <c r="O55" s="26"/>
-      <c r="P55" s="51"/>
-      <c r="Q55" t="s">
-        <v>201</v>
+      <c r="P55" s="43"/>
+      <c r="Q55" s="10" t="s">
+        <v>192</v>
       </c>
       <c r="R55" s="12"/>
       <c r="S55" s="27"/>
       <c r="T55" s="29"/>
-      <c r="U55" s="34">
-        <v>4219</v>
+      <c r="U55" s="34" t="s">
+        <v>37</v>
       </c>
       <c r="V55" s="38"/>
       <c r="W55" s="32"/>
       <c r="X55" s="31"/>
-      <c r="Y55" s="43">
-        <v>1455</v>
-      </c>
-      <c r="Z55" s="44"/>
-      <c r="AA55" s="45"/>
-      <c r="AB55" s="50"/>
-    </row>
-    <row r="56" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E56" s="8">
-        <v>20340</v>
-      </c>
-      <c r="F56" s="9"/>
-      <c r="G56" s="40"/>
-      <c r="H56" s="23"/>
-      <c r="I56" s="58">
-        <v>1182211</v>
-      </c>
-      <c r="K56" s="41"/>
-      <c r="L56" s="16"/>
-      <c r="O56" s="26"/>
-      <c r="Q56" t="s">
-        <v>202</v>
-      </c>
-      <c r="S56" s="27"/>
-      <c r="T56" s="29"/>
-      <c r="V56" s="37"/>
-      <c r="W56" s="32"/>
-      <c r="X56" s="31"/>
-      <c r="Y56" s="43">
-        <v>390</v>
-      </c>
-      <c r="AA56" s="45"/>
-      <c r="AB56" s="50"/>
-    </row>
-    <row r="57" spans="1:28" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+      <c r="I56" s="50">
+        <v>2030393</v>
+      </c>
+      <c r="L56" s="24"/>
+      <c r="M56" s="46"/>
+      <c r="Q56" s="10" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="E57" s="8">
-        <v>20478</v>
+        <v>75104</v>
       </c>
       <c r="F57" s="9"/>
       <c r="G57" s="40"/>
       <c r="H57" s="23"/>
-      <c r="I57" s="58">
-        <v>4868220</v>
+      <c r="I57" s="50">
+        <v>1164375</v>
       </c>
       <c r="K57" s="41"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="61">
-        <v>6419329</v>
-      </c>
-      <c r="N57" s="14"/>
-      <c r="O57" s="26"/>
-      <c r="P57" s="51"/>
-      <c r="Q57" t="s">
-        <v>203</v>
+      <c r="L57" s="24"/>
+      <c r="M57" s="46"/>
+      <c r="Q57" s="10" t="s">
+        <v>194</v>
       </c>
       <c r="R57" s="12"/>
       <c r="S57" s="27"/>
       <c r="T57" s="29"/>
       <c r="U57" s="34">
-        <v>8125</v>
+        <v>4176</v>
       </c>
       <c r="V57" s="38"/>
       <c r="W57" s="32"/>
       <c r="X57" s="31"/>
-      <c r="Y57" s="43">
-        <v>404</v>
-      </c>
-      <c r="Z57" s="44"/>
-      <c r="AA57" s="45"/>
-      <c r="AB57" s="50"/>
-    </row>
-    <row r="58" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E58" s="8">
-        <v>34298</v>
+        <v>75736</v>
       </c>
       <c r="F58" s="9"/>
       <c r="G58" s="40"/>
       <c r="H58" s="23"/>
-      <c r="I58" s="58">
-        <v>3758778</v>
+      <c r="I58" s="50">
+        <v>1354135</v>
       </c>
       <c r="K58" s="41"/>
       <c r="L58" s="16"/>
-      <c r="M58" s="54"/>
+      <c r="M58" s="47">
+        <v>1457100</v>
+      </c>
+      <c r="N58" s="14"/>
       <c r="O58" s="26"/>
-      <c r="Q58" t="s">
-        <v>204</v>
+      <c r="P58" s="43"/>
+      <c r="Q58" s="10" t="s">
+        <v>195</v>
       </c>
       <c r="R58" s="12"/>
       <c r="S58" s="27"/>
       <c r="T58" s="29"/>
       <c r="U58" s="34">
-        <v>8168</v>
+        <v>4184</v>
       </c>
       <c r="V58" s="38"/>
       <c r="W58" s="32"/>
       <c r="X58" s="31"/>
-      <c r="Y58" s="43">
-        <v>403</v>
-      </c>
-      <c r="Z58" s="44"/>
-      <c r="AA58" s="45"/>
-      <c r="AB58" s="50"/>
-    </row>
-    <row r="59" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>38</v>
+        <v>114</v>
+      </c>
+      <c r="E59" s="8">
+        <v>74844</v>
       </c>
       <c r="F59" s="9"/>
       <c r="G59" s="40"/>
       <c r="H59" s="23"/>
-      <c r="I59" s="58">
-        <v>6056907</v>
+      <c r="I59" s="50">
+        <v>9173196</v>
       </c>
       <c r="K59" s="41"/>
-      <c r="L59" s="16"/>
+      <c r="L59" s="24"/>
+      <c r="M59" s="53">
+        <v>2016442</v>
+      </c>
       <c r="N59" s="14"/>
       <c r="O59" s="26"/>
-      <c r="P59" s="51"/>
-      <c r="Q59" t="s">
-        <v>205</v>
+      <c r="P59" s="43"/>
+      <c r="Q59" s="10" t="s">
+        <v>196</v>
       </c>
       <c r="R59" s="12"/>
       <c r="S59" s="27"/>
       <c r="T59" s="29"/>
       <c r="U59" s="34">
-        <v>8243</v>
+        <v>4219</v>
       </c>
       <c r="V59" s="38"/>
       <c r="W59" s="32"/>
       <c r="X59" s="31"/>
-      <c r="Y59" s="43">
-        <v>420</v>
-      </c>
-      <c r="Z59" s="44"/>
-      <c r="AA59" s="45"/>
-      <c r="AB59" s="50"/>
-    </row>
-    <row r="60" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E60" s="8" t="s">
-        <v>43</v>
+        <v>118</v>
+      </c>
+      <c r="E60" s="8">
+        <v>20340</v>
       </c>
       <c r="F60" s="9"/>
       <c r="G60" s="40"/>
       <c r="H60" s="23"/>
-      <c r="I60" s="58">
-        <v>7350788</v>
+      <c r="I60" s="50">
+        <v>1182211</v>
       </c>
       <c r="K60" s="41"/>
       <c r="L60" s="16"/>
-      <c r="M60" s="61">
-        <v>1326438</v>
-      </c>
-      <c r="N60" s="14"/>
+      <c r="M60" s="46"/>
       <c r="O60" s="26"/>
-      <c r="P60" s="51"/>
-      <c r="Q60" t="s">
-        <v>206</v>
+      <c r="Q60" s="10" t="s">
+        <v>197</v>
       </c>
       <c r="S60" s="27"/>
       <c r="T60" s="29"/>
-      <c r="U60" s="34">
-        <v>8169</v>
-      </c>
-      <c r="V60" s="38"/>
+      <c r="V60" s="37"/>
       <c r="W60" s="32"/>
       <c r="X60" s="31"/>
-      <c r="Y60" s="43">
-        <v>244</v>
-      </c>
-      <c r="Z60" s="44"/>
-      <c r="AA60" s="45"/>
-      <c r="AB60" s="50"/>
-    </row>
-    <row r="61" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E61" s="8" t="s">
-        <v>39</v>
+        <v>88</v>
+      </c>
+      <c r="E61" s="8">
+        <v>20478</v>
       </c>
       <c r="F61" s="9"/>
       <c r="G61" s="40"/>
       <c r="H61" s="23"/>
-      <c r="I61" s="58">
-        <v>8313967</v>
+      <c r="I61" s="50">
+        <v>4868220</v>
       </c>
       <c r="K61" s="41"/>
       <c r="L61" s="16"/>
-      <c r="M61" s="55"/>
+      <c r="M61" s="53">
+        <v>6419329</v>
+      </c>
       <c r="N61" s="14"/>
       <c r="O61" s="26"/>
-      <c r="P61" s="51"/>
-      <c r="Q61" t="s">
-        <v>207</v>
+      <c r="P61" s="43"/>
+      <c r="Q61" s="10" t="s">
+        <v>198</v>
       </c>
       <c r="R61" s="12"/>
       <c r="S61" s="27"/>
       <c r="T61" s="29"/>
       <c r="U61" s="34">
-        <v>8083</v>
+        <v>8125</v>
       </c>
       <c r="V61" s="38"/>
       <c r="W61" s="32"/>
       <c r="X61" s="31"/>
-      <c r="Y61" s="43">
-        <v>490</v>
-      </c>
-      <c r="Z61" s="44"/>
-      <c r="AA61" s="45"/>
-      <c r="AB61" s="50"/>
-    </row>
-    <row r="62" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>40</v>
+        <v>87</v>
+      </c>
+      <c r="E62" s="8">
+        <v>34298</v>
       </c>
       <c r="F62" s="9"/>
       <c r="G62" s="40"/>
       <c r="H62" s="23"/>
-      <c r="L62" s="24"/>
-      <c r="M62" s="54"/>
-      <c r="Q62" t="s">
-        <v>208</v>
-      </c>
+      <c r="I62" s="50">
+        <v>3758778</v>
+      </c>
+      <c r="K62" s="41"/>
+      <c r="L62" s="16"/>
+      <c r="M62" s="46"/>
+      <c r="O62" s="26"/>
+      <c r="Q62" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="R62" s="12"/>
       <c r="S62" s="27"/>
       <c r="T62" s="29"/>
       <c r="U62" s="34">
-        <v>8080</v>
+        <v>8168</v>
       </c>
       <c r="V62" s="38"/>
       <c r="W62" s="32"/>
       <c r="X62" s="31"/>
-      <c r="Y62" s="43">
-        <v>505</v>
-      </c>
-      <c r="Z62" s="44"/>
-      <c r="AA62" s="45"/>
-      <c r="AB62" s="50"/>
-    </row>
-    <row r="63" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="I63" s="58" t="s">
-        <v>150</v>
-      </c>
-      <c r="L63" s="24"/>
-      <c r="Q63" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="64" spans="1:28" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F63" s="9"/>
+      <c r="G63" s="40"/>
+      <c r="H63" s="23"/>
+      <c r="I63" s="50">
+        <v>6056907</v>
+      </c>
+      <c r="K63" s="41"/>
+      <c r="L63" s="16"/>
+      <c r="M63" s="46"/>
+      <c r="N63" s="14"/>
+      <c r="O63" s="26"/>
+      <c r="P63" s="43"/>
+      <c r="Q63" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="R63" s="12"/>
+      <c r="S63" s="27"/>
+      <c r="T63" s="29"/>
+      <c r="U63" s="34">
+        <v>8243</v>
+      </c>
+      <c r="V63" s="38"/>
+      <c r="W63" s="32"/>
+      <c r="X63" s="31"/>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F64" s="9"/>
       <c r="G64" s="40"/>
       <c r="H64" s="23"/>
-      <c r="I64" s="58">
-        <v>1094721</v>
+      <c r="I64" s="50">
+        <v>7350788</v>
       </c>
       <c r="K64" s="41"/>
       <c r="L64" s="16"/>
-      <c r="M64" s="61">
-        <v>8326696</v>
+      <c r="M64" s="53">
+        <v>1326438</v>
       </c>
       <c r="N64" s="14"/>
       <c r="O64" s="26"/>
-      <c r="P64" s="51"/>
-      <c r="Q64" t="s">
-        <v>210</v>
-      </c>
-      <c r="R64" s="12"/>
+      <c r="P64" s="43"/>
+      <c r="Q64" s="10" t="s">
+        <v>201</v>
+      </c>
       <c r="S64" s="27"/>
       <c r="T64" s="29"/>
       <c r="U64" s="34">
-        <v>8086</v>
+        <v>8169</v>
       </c>
       <c r="V64" s="38"/>
       <c r="W64" s="32"/>
       <c r="X64" s="31"/>
-      <c r="Y64" s="43">
-        <v>455</v>
-      </c>
-      <c r="Z64" s="44"/>
-      <c r="AA64" s="45"/>
-      <c r="AB64" s="50"/>
-    </row>
-    <row r="65" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F65" s="9"/>
       <c r="G65" s="40"/>
       <c r="H65" s="23"/>
-      <c r="I65" s="58">
-        <v>6846554</v>
+      <c r="I65" s="50">
+        <v>8313967</v>
       </c>
       <c r="K65" s="41"/>
       <c r="L65" s="16"/>
-      <c r="M65" s="54"/>
-      <c r="Q65" t="s">
-        <v>211</v>
-      </c>
+      <c r="M65" s="47"/>
+      <c r="N65" s="14"/>
+      <c r="O65" s="26"/>
+      <c r="P65" s="43"/>
+      <c r="Q65" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="R65" s="12"/>
       <c r="S65" s="27"/>
       <c r="T65" s="29"/>
-      <c r="V65" s="37"/>
+      <c r="U65" s="34">
+        <v>8083</v>
+      </c>
+      <c r="V65" s="38"/>
       <c r="W65" s="32"/>
       <c r="X65" s="31"/>
-      <c r="Y65" s="43">
-        <v>500</v>
-      </c>
-      <c r="AA65" s="45"/>
-      <c r="AB65" s="50"/>
-    </row>
-    <row r="66" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="I66" s="58" t="s">
-        <v>151</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F66" s="9"/>
+      <c r="G66" s="40"/>
+      <c r="H66" s="23"/>
       <c r="L66" s="24"/>
-      <c r="M66" s="54"/>
-      <c r="Q66" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="67" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="M66" s="46"/>
+      <c r="Q66" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="S66" s="27"/>
+      <c r="T66" s="29"/>
+      <c r="U66" s="34">
+        <v>8080</v>
+      </c>
+      <c r="V66" s="38"/>
+      <c r="W66" s="32"/>
+      <c r="X66" s="31"/>
+    </row>
+    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>139</v>
+        <v>70</v>
+      </c>
+      <c r="I67" s="50" t="s">
+        <v>145</v>
       </c>
       <c r="L67" s="24"/>
-      <c r="M67" s="54"/>
-      <c r="Q67" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="68" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="M67" s="46"/>
+      <c r="Q67" s="10" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="68" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H68" s="22"/>
-      <c r="L68" s="24"/>
-      <c r="M68" s="54"/>
-      <c r="Q68" t="s">
-        <v>214</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F68" s="9"/>
+      <c r="G68" s="40"/>
+      <c r="H68" s="23"/>
+      <c r="I68" s="50">
+        <v>1094721</v>
+      </c>
+      <c r="K68" s="41"/>
+      <c r="L68" s="16"/>
+      <c r="M68" s="53">
+        <v>8326696</v>
+      </c>
+      <c r="N68" s="14"/>
+      <c r="O68" s="26"/>
+      <c r="P68" s="43"/>
+      <c r="Q68" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="R68" s="12"/>
       <c r="S68" s="27"/>
       <c r="T68" s="29"/>
-      <c r="V68" s="37"/>
+      <c r="U68" s="34">
+        <v>8086</v>
+      </c>
+      <c r="V68" s="38"/>
       <c r="W68" s="32"/>
       <c r="X68" s="31"/>
-      <c r="Y68" s="43" t="s">
-        <v>129</v>
-      </c>
-      <c r="AA68" s="45"/>
-      <c r="AB68" s="46"/>
-    </row>
-    <row r="69" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="E69" s="8">
-        <v>78424</v>
+        <v>92</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>42</v>
       </c>
       <c r="F69" s="9"/>
       <c r="G69" s="40"/>
       <c r="H69" s="23"/>
-      <c r="I69" s="58">
-        <v>1008382</v>
+      <c r="I69" s="50">
+        <v>6846554</v>
       </c>
       <c r="K69" s="41"/>
       <c r="L69" s="16"/>
-      <c r="M69" s="54"/>
-      <c r="N69" s="14"/>
-      <c r="O69" s="26"/>
-      <c r="Q69" t="s">
-        <v>215</v>
-      </c>
-      <c r="R69" s="12"/>
+      <c r="M69" s="46"/>
+      <c r="Q69" s="10" t="s">
+        <v>206</v>
+      </c>
       <c r="S69" s="27"/>
       <c r="T69" s="29"/>
-      <c r="U69" s="34">
-        <v>8275</v>
-      </c>
-      <c r="V69" s="38"/>
+      <c r="V69" s="37"/>
       <c r="W69" s="32"/>
       <c r="X69" s="31"/>
-      <c r="Y69" s="43">
-        <v>828</v>
-      </c>
-      <c r="Z69" s="44"/>
-      <c r="AA69" s="45"/>
-      <c r="AB69" s="50"/>
-    </row>
-    <row r="70" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="E70" s="8">
-        <v>75310</v>
-      </c>
-      <c r="F70" s="9"/>
-      <c r="G70" s="40"/>
-      <c r="H70" s="23"/>
-      <c r="I70" s="58">
-        <v>4249389</v>
-      </c>
-      <c r="K70" s="41"/>
-      <c r="L70" s="16"/>
-      <c r="M70" s="54"/>
-      <c r="Q70" t="s">
-        <v>216</v>
-      </c>
-      <c r="R70" s="12"/>
-      <c r="S70" s="27"/>
-      <c r="T70" s="29"/>
-      <c r="U70" s="34">
-        <v>8110</v>
-      </c>
-      <c r="V70" s="38"/>
-      <c r="W70" s="32"/>
-      <c r="X70" s="31"/>
-      <c r="Y70" s="43">
-        <v>563</v>
-      </c>
-      <c r="Z70" s="44"/>
-      <c r="AA70" s="45"/>
-      <c r="AB70" s="50"/>
-    </row>
-    <row r="71" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A71" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B71" s="3"/>
-      <c r="C71" s="3"/>
-      <c r="D71" s="35"/>
-      <c r="E71" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F71" s="9"/>
-      <c r="G71" s="40"/>
-      <c r="H71" s="23"/>
+        <v>133</v>
+      </c>
+      <c r="I70" s="50" t="s">
+        <v>146</v>
+      </c>
+      <c r="L70" s="24"/>
+      <c r="M70" s="46"/>
+      <c r="Q70" s="10" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>134</v>
+      </c>
       <c r="L71" s="24"/>
-      <c r="M71" s="54"/>
-      <c r="N71" s="14"/>
-      <c r="O71" s="26"/>
-      <c r="P71" s="51"/>
-      <c r="Q71" s="82" t="s">
-        <v>217</v>
-      </c>
-      <c r="R71" s="12"/>
-      <c r="S71" s="27"/>
-      <c r="T71" s="29"/>
-      <c r="U71" s="34">
-        <v>8560</v>
-      </c>
-      <c r="V71" s="38"/>
-      <c r="W71" s="32"/>
-      <c r="X71" s="31"/>
-      <c r="Y71" s="43">
-        <v>570</v>
-      </c>
-      <c r="Z71" s="44"/>
-      <c r="AA71" s="45"/>
-      <c r="AB71" s="50"/>
-    </row>
-    <row r="72" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="M71" s="46"/>
+      <c r="Q71" s="10" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="72" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="E72" s="8">
-        <v>70646</v>
-      </c>
-      <c r="F72" s="9"/>
-      <c r="G72" s="40"/>
-      <c r="H72" s="23"/>
-      <c r="I72" s="58">
-        <v>1420330</v>
-      </c>
-      <c r="K72" s="41"/>
-      <c r="L72" s="16"/>
-      <c r="M72" s="55">
-        <v>1028511</v>
-      </c>
-      <c r="N72" s="14"/>
-      <c r="O72" s="26"/>
-      <c r="P72" s="51"/>
-      <c r="Q72" t="s">
-        <v>218</v>
-      </c>
-      <c r="R72" s="12"/>
+        <v>67</v>
+      </c>
+      <c r="H72" s="22"/>
+      <c r="L72" s="24"/>
+      <c r="M72" s="46"/>
+      <c r="Q72" s="10" t="s">
+        <v>209</v>
+      </c>
       <c r="S72" s="27"/>
       <c r="T72" s="29"/>
-      <c r="U72" s="34">
-        <v>8127</v>
-      </c>
-      <c r="V72" s="38"/>
+      <c r="V72" s="37"/>
       <c r="W72" s="32"/>
       <c r="X72" s="31"/>
-      <c r="Y72" s="43">
-        <v>565</v>
-      </c>
-      <c r="Z72" s="44"/>
-      <c r="AA72" s="45"/>
-      <c r="AB72" s="50"/>
-    </row>
-    <row r="73" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E73" s="8" t="s">
-        <v>48</v>
+        <v>109</v>
+      </c>
+      <c r="E73" s="8">
+        <v>78424</v>
       </c>
       <c r="F73" s="9"/>
       <c r="G73" s="40"/>
       <c r="H73" s="23"/>
-      <c r="I73" s="58">
-        <v>9927799</v>
+      <c r="I73" s="50">
+        <v>1008382</v>
       </c>
       <c r="K73" s="41"/>
       <c r="L73" s="16"/>
-      <c r="M73" s="55">
-        <v>2012150</v>
-      </c>
+      <c r="M73" s="46"/>
       <c r="N73" s="14"/>
       <c r="O73" s="26"/>
-      <c r="P73" s="51"/>
-      <c r="Q73" t="s">
-        <v>219</v>
+      <c r="Q73" s="10" t="s">
+        <v>210</v>
       </c>
       <c r="R73" s="12"/>
       <c r="S73" s="27"/>
       <c r="T73" s="29"/>
       <c r="U73" s="34">
-        <v>8058</v>
+        <v>8275</v>
       </c>
       <c r="V73" s="38"/>
       <c r="W73" s="32"/>
       <c r="X73" s="31"/>
-      <c r="Y73" s="43">
-        <v>605</v>
-      </c>
-      <c r="Z73" s="44"/>
-      <c r="AA73" s="45"/>
-      <c r="AB73" s="50"/>
-    </row>
-    <row r="74" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="74" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="E74" s="8">
-        <v>75336</v>
+        <v>75310</v>
       </c>
       <c r="F74" s="9"/>
-      <c r="G74" s="9"/>
-      <c r="H74" s="22"/>
-      <c r="I74" s="58">
-        <v>1745161</v>
+      <c r="G74" s="40"/>
+      <c r="H74" s="23"/>
+      <c r="I74" s="50">
+        <v>4249389</v>
       </c>
       <c r="K74" s="41"/>
       <c r="L74" s="16"/>
-      <c r="M74" s="55">
-        <v>1028515</v>
-      </c>
-      <c r="N74" s="14"/>
-      <c r="O74" s="26"/>
-      <c r="P74" s="51"/>
-      <c r="Q74" t="s">
-        <v>220</v>
-      </c>
+      <c r="M74" s="46"/>
+      <c r="Q74" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="R74" s="12"/>
       <c r="S74" s="27"/>
       <c r="T74" s="29"/>
       <c r="U74" s="34">
-        <v>8465</v>
+        <v>8110</v>
       </c>
       <c r="V74" s="38"/>
       <c r="W74" s="32"/>
       <c r="X74" s="31"/>
-      <c r="Y74" s="43">
-        <v>575</v>
-      </c>
-      <c r="Z74" s="44"/>
-      <c r="AA74" s="45"/>
-      <c r="AB74" s="50"/>
-    </row>
-    <row r="75" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>125</v>
-      </c>
+    </row>
+    <row r="75" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="35"/>
       <c r="E75" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F75" s="9"/>
       <c r="G75" s="40"/>
       <c r="H75" s="23"/>
-      <c r="I75" s="58">
-        <v>4615704</v>
-      </c>
-      <c r="K75" s="41"/>
-      <c r="L75" s="16"/>
-      <c r="M75" s="54"/>
-      <c r="Q75" t="s">
-        <v>221</v>
-      </c>
+      <c r="L75" s="24"/>
+      <c r="M75" s="46"/>
+      <c r="N75" s="14"/>
+      <c r="O75" s="26"/>
+      <c r="P75" s="43"/>
+      <c r="Q75" s="52" t="s">
+        <v>212</v>
+      </c>
+      <c r="R75" s="12"/>
       <c r="S75" s="27"/>
       <c r="T75" s="29"/>
-      <c r="V75" s="37"/>
+      <c r="U75" s="34">
+        <v>8560</v>
+      </c>
+      <c r="V75" s="38"/>
       <c r="W75" s="32"/>
       <c r="X75" s="31"/>
-      <c r="Y75" s="43">
-        <v>585</v>
-      </c>
-      <c r="AA75" s="45"/>
-      <c r="AB75" s="50"/>
-    </row>
-    <row r="76" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A76" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="B76" s="3"/>
-      <c r="C76" s="3"/>
-      <c r="D76" s="35"/>
-      <c r="E76" s="8"/>
+    </row>
+    <row r="76" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E76" s="8">
+        <v>70646</v>
+      </c>
       <c r="F76" s="9"/>
-      <c r="H76" s="22"/>
-      <c r="L76" s="24"/>
-      <c r="M76" s="54"/>
+      <c r="G76" s="40"/>
+      <c r="H76" s="23"/>
+      <c r="I76" s="50">
+        <v>1420330</v>
+      </c>
+      <c r="K76" s="41"/>
+      <c r="L76" s="16"/>
+      <c r="M76" s="47">
+        <v>1028511</v>
+      </c>
       <c r="N76" s="14"/>
       <c r="O76" s="26"/>
-      <c r="Q76" s="82"/>
+      <c r="P76" s="43"/>
+      <c r="Q76" s="10" t="s">
+        <v>213</v>
+      </c>
       <c r="R76" s="12"/>
       <c r="S76" s="27"/>
       <c r="T76" s="29"/>
+      <c r="U76" s="34">
+        <v>8127</v>
+      </c>
       <c r="V76" s="38"/>
+      <c r="W76" s="32"/>
       <c r="X76" s="31"/>
-      <c r="Z76" s="44"/>
-      <c r="AB76" s="50"/>
-    </row>
-    <row r="77" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="77" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E77" s="8">
-        <v>75690</v>
+        <v>98</v>
+      </c>
+      <c r="E77" s="8" t="s">
+        <v>48</v>
       </c>
       <c r="F77" s="9"/>
       <c r="G77" s="40"/>
       <c r="H77" s="23"/>
-      <c r="I77" s="58">
-        <v>7413057</v>
+      <c r="I77" s="50">
+        <v>9927799</v>
       </c>
       <c r="K77" s="41"/>
       <c r="L77" s="16"/>
-      <c r="M77" s="55">
-        <v>4221933</v>
+      <c r="M77" s="47">
+        <v>2012150</v>
       </c>
       <c r="N77" s="14"/>
       <c r="O77" s="26"/>
-      <c r="P77" s="51"/>
-      <c r="Q77" t="s">
-        <v>222</v>
+      <c r="P77" s="43"/>
+      <c r="Q77" s="10" t="s">
+        <v>214</v>
       </c>
       <c r="R77" s="12"/>
       <c r="S77" s="27"/>
       <c r="T77" s="29"/>
+      <c r="U77" s="34">
+        <v>8058</v>
+      </c>
       <c r="V77" s="38"/>
       <c r="W77" s="32"/>
       <c r="X77" s="31"/>
-      <c r="Y77" s="43">
-        <v>1650</v>
-      </c>
-      <c r="Z77" s="44"/>
-      <c r="AA77" s="45"/>
-      <c r="AB77" s="50"/>
-    </row>
-    <row r="78" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="E78" s="8">
-        <v>77278</v>
+        <v>75336</v>
       </c>
       <c r="F78" s="9"/>
-      <c r="G78" s="40"/>
-      <c r="H78" s="23"/>
-      <c r="L78" s="24"/>
-      <c r="M78" s="54"/>
-      <c r="Q78" t="s">
-        <v>223</v>
-      </c>
-      <c r="R78" s="12"/>
+      <c r="G78" s="9"/>
+      <c r="H78" s="22"/>
+      <c r="I78" s="50">
+        <v>1745161</v>
+      </c>
+      <c r="K78" s="41"/>
+      <c r="L78" s="16"/>
+      <c r="M78" s="47">
+        <v>1028515</v>
+      </c>
+      <c r="N78" s="14"/>
+      <c r="O78" s="26"/>
+      <c r="P78" s="43"/>
+      <c r="Q78" s="10" t="s">
+        <v>215</v>
+      </c>
       <c r="S78" s="27"/>
       <c r="T78" s="29"/>
       <c r="U78" s="34">
-        <v>4060</v>
+        <v>8465</v>
       </c>
       <c r="V78" s="38"/>
       <c r="W78" s="32"/>
       <c r="X78" s="31"/>
-      <c r="Z78" s="44"/>
-      <c r="AA78" s="45"/>
-      <c r="AB78" s="50"/>
-    </row>
-    <row r="79" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="79" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F79" s="9"/>
       <c r="G79" s="40"/>
       <c r="H79" s="23"/>
-      <c r="L79" s="24"/>
-      <c r="Q79"/>
+      <c r="I79" s="50">
+        <v>4615704</v>
+      </c>
+      <c r="K79" s="41"/>
+      <c r="L79" s="16"/>
+      <c r="M79" s="46"/>
+      <c r="Q79" s="10" t="s">
+        <v>216</v>
+      </c>
       <c r="S79" s="27"/>
       <c r="T79" s="29"/>
       <c r="V79" s="37"/>
       <c r="W79" s="32"/>
       <c r="X79" s="31"/>
-      <c r="AA79" s="45"/>
-      <c r="AB79" s="50"/>
-    </row>
-    <row r="80" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E80" s="8" t="s">
-        <v>51</v>
-      </c>
+    </row>
+    <row r="80" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="35"/>
       <c r="F80" s="9"/>
-      <c r="G80" s="40"/>
-      <c r="H80" s="23"/>
-      <c r="I80" s="58">
-        <v>1313154</v>
-      </c>
-      <c r="K80" s="41"/>
-      <c r="L80" s="16"/>
-      <c r="M80" s="54"/>
+      <c r="H80" s="22"/>
+      <c r="L80" s="24"/>
+      <c r="M80" s="46"/>
+      <c r="N80" s="14"/>
       <c r="O80" s="26"/>
-      <c r="Q80" t="s">
-        <v>224</v>
-      </c>
+      <c r="Q80" s="52"/>
       <c r="R80" s="12"/>
       <c r="S80" s="27"/>
       <c r="T80" s="29"/>
-      <c r="U80" s="34">
-        <v>8484</v>
-      </c>
       <c r="V80" s="38"/>
-      <c r="W80" s="32"/>
       <c r="X80" s="31"/>
-      <c r="Y80" s="43">
-        <v>651</v>
-      </c>
-      <c r="Z80" s="44"/>
-      <c r="AA80" s="45"/>
-      <c r="AB80" s="50"/>
-    </row>
-    <row r="81" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="81" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>102</v>
+        <v>49</v>
       </c>
       <c r="E81" s="8">
-        <v>34768</v>
+        <v>75690</v>
       </c>
       <c r="F81" s="9"/>
-      <c r="G81" s="9"/>
-      <c r="H81" s="22"/>
-      <c r="I81" s="58">
-        <v>8481756</v>
+      <c r="G81" s="40"/>
+      <c r="H81" s="23"/>
+      <c r="I81" s="50">
+        <v>7413057</v>
       </c>
       <c r="K81" s="41"/>
       <c r="L81" s="16"/>
-      <c r="M81" s="55">
-        <v>8010498</v>
+      <c r="M81" s="47">
+        <v>4221933</v>
       </c>
       <c r="N81" s="14"/>
       <c r="O81" s="26"/>
-      <c r="P81" s="51"/>
-      <c r="Q81" t="s">
-        <v>225</v>
+      <c r="P81" s="43"/>
+      <c r="Q81" s="10" t="s">
+        <v>217</v>
       </c>
       <c r="R81" s="12"/>
       <c r="S81" s="27"/>
       <c r="T81" s="29"/>
-      <c r="U81" s="34">
-        <v>8277</v>
-      </c>
       <c r="V81" s="38"/>
       <c r="W81" s="32"/>
       <c r="X81" s="31"/>
-      <c r="Y81" s="43">
-        <v>660</v>
-      </c>
-      <c r="Z81" s="44"/>
-      <c r="AA81" s="45"/>
-      <c r="AB81" s="50"/>
-    </row>
-    <row r="82" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="82" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E82" s="8" t="s">
-        <v>52</v>
+        <v>100</v>
+      </c>
+      <c r="E82" s="8">
+        <v>77278</v>
       </c>
       <c r="F82" s="9"/>
       <c r="G82" s="40"/>
       <c r="H82" s="23"/>
-      <c r="I82" s="58">
-        <v>1008465</v>
-      </c>
-      <c r="K82" s="41"/>
-      <c r="L82" s="16"/>
-      <c r="M82" s="54"/>
-      <c r="O82" s="26"/>
-      <c r="Q82" t="s">
-        <v>226</v>
-      </c>
+      <c r="L82" s="24"/>
+      <c r="M82" s="46"/>
+      <c r="Q82" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="R82" s="12"/>
       <c r="S82" s="27"/>
       <c r="T82" s="29"/>
-      <c r="V82" s="37"/>
+      <c r="U82" s="34">
+        <v>4060</v>
+      </c>
+      <c r="V82" s="38"/>
       <c r="W82" s="32"/>
       <c r="X82" s="31"/>
-      <c r="Y82" s="43">
-        <v>706</v>
-      </c>
-      <c r="AA82" s="45"/>
-      <c r="AB82" s="50"/>
-    </row>
-    <row r="83" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="83" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>141</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="E83" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F83" s="9"/>
+      <c r="G83" s="40"/>
+      <c r="H83" s="23"/>
       <c r="L83" s="24"/>
-      <c r="M83" s="54"/>
-      <c r="Q83" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="84" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="M83" s="46"/>
+      <c r="S83" s="27"/>
+      <c r="T83" s="29"/>
+      <c r="V83" s="37"/>
+      <c r="W83" s="32"/>
+      <c r="X83" s="31"/>
+    </row>
+    <row r="84" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E84" s="8">
-        <v>78025</v>
+        <v>101</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>51</v>
       </c>
       <c r="F84" s="9"/>
-      <c r="H84" s="22"/>
-      <c r="I84" s="58">
-        <v>6894232</v>
+      <c r="G84" s="40"/>
+      <c r="H84" s="23"/>
+      <c r="I84" s="50">
+        <v>1313154</v>
       </c>
       <c r="K84" s="41"/>
       <c r="L84" s="16"/>
-      <c r="M84" s="54"/>
-      <c r="Q84" t="s">
-        <v>228</v>
+      <c r="M84" s="46"/>
+      <c r="O84" s="26"/>
+      <c r="Q84" s="10" t="s">
+        <v>219</v>
       </c>
       <c r="R84" s="12"/>
       <c r="S84" s="27"/>
       <c r="T84" s="29"/>
+      <c r="U84" s="34">
+        <v>8484</v>
+      </c>
       <c r="V84" s="38"/>
       <c r="W84" s="32"/>
       <c r="X84" s="31"/>
-      <c r="Y84" s="43">
-        <v>805</v>
-      </c>
-      <c r="Z84" s="44"/>
-      <c r="AA84" s="45"/>
-      <c r="AB84" s="50"/>
-    </row>
-    <row r="85" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="85" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="L85" s="24"/>
-      <c r="M85" s="54"/>
-      <c r="Q85" t="s">
-        <v>229</v>
-      </c>
-      <c r="Y85" s="43" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="86" spans="1:28" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+      <c r="E85" s="8">
+        <v>34768</v>
+      </c>
+      <c r="F85" s="9"/>
+      <c r="G85" s="9"/>
+      <c r="H85" s="22"/>
+      <c r="I85" s="50">
+        <v>8481756</v>
+      </c>
+      <c r="K85" s="41"/>
+      <c r="L85" s="16"/>
+      <c r="M85" s="47">
+        <v>8010498</v>
+      </c>
+      <c r="N85" s="14"/>
+      <c r="O85" s="26"/>
+      <c r="P85" s="43"/>
+      <c r="Q85" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="R85" s="12"/>
+      <c r="S85" s="27"/>
+      <c r="T85" s="29"/>
+      <c r="U85" s="34">
+        <v>8277</v>
+      </c>
+      <c r="V85" s="38"/>
+      <c r="W85" s="32"/>
+      <c r="X85" s="31"/>
+    </row>
+    <row r="86" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H86" s="22"/>
-      <c r="L86" s="24"/>
-      <c r="M86" s="54"/>
-      <c r="Q86" t="s">
-        <v>230</v>
-      </c>
-      <c r="Y86" s="43" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="87" spans="1:28" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E86" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F86" s="9"/>
+      <c r="G86" s="40"/>
+      <c r="H86" s="23"/>
+      <c r="I86" s="50">
+        <v>1008465</v>
+      </c>
+      <c r="K86" s="41"/>
+      <c r="L86" s="16"/>
+      <c r="M86" s="46"/>
+      <c r="O86" s="26"/>
+      <c r="Q86" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="S86" s="27"/>
+      <c r="T86" s="29"/>
+      <c r="V86" s="37"/>
+      <c r="W86" s="32"/>
+      <c r="X86" s="31"/>
+    </row>
+    <row r="87" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E87" s="8">
-        <v>78126</v>
-      </c>
-      <c r="F87" s="9"/>
-      <c r="G87" s="40"/>
-      <c r="H87" s="23"/>
-      <c r="I87" s="58">
-        <v>2036598</v>
-      </c>
-      <c r="K87" s="41"/>
-      <c r="L87" s="16"/>
-      <c r="M87" s="55">
-        <v>4074472</v>
-      </c>
-      <c r="N87" s="14"/>
-      <c r="O87" s="26"/>
-      <c r="P87" s="51"/>
-      <c r="Q87" t="s">
-        <v>231</v>
-      </c>
-      <c r="R87" s="12"/>
-      <c r="S87" s="27"/>
-      <c r="T87" s="29"/>
-      <c r="U87" s="34">
-        <v>8142</v>
-      </c>
-      <c r="V87" s="38"/>
-      <c r="W87" s="32"/>
-      <c r="X87" s="31"/>
-      <c r="Y87" s="43">
-        <v>865</v>
-      </c>
-      <c r="Z87" s="44"/>
-      <c r="AA87" s="45"/>
-      <c r="AB87" s="50"/>
-    </row>
-    <row r="88" spans="1:28" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="L87" s="24"/>
+      <c r="M87" s="46"/>
+      <c r="Q87" s="10" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="88" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="E88" s="8">
-        <v>39142</v>
+        <v>78025</v>
       </c>
       <c r="F88" s="9"/>
-      <c r="G88" s="40"/>
-      <c r="H88" s="23"/>
-      <c r="I88" s="58">
-        <v>6235501</v>
+      <c r="H88" s="22"/>
+      <c r="I88" s="50">
+        <v>6894232</v>
       </c>
       <c r="K88" s="41"/>
       <c r="L88" s="16"/>
-      <c r="M88" s="56">
-        <v>1205582</v>
-      </c>
-      <c r="N88" s="14"/>
-      <c r="O88" s="26"/>
-      <c r="Q88" t="s">
-        <v>232</v>
+      <c r="M88" s="46"/>
+      <c r="Q88" s="10" t="s">
+        <v>223</v>
       </c>
       <c r="R88" s="12"/>
       <c r="S88" s="27"/>
       <c r="T88" s="29"/>
-      <c r="U88" s="34">
-        <v>4193</v>
-      </c>
       <c r="V88" s="38"/>
       <c r="W88" s="32"/>
       <c r="X88" s="31"/>
-      <c r="Y88" s="43">
-        <v>1150</v>
-      </c>
-      <c r="Z88" s="44"/>
-      <c r="AA88" s="45"/>
-      <c r="AB88" s="50"/>
-    </row>
-    <row r="89" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="89" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="L89" s="24"/>
+      <c r="M89" s="46"/>
+      <c r="Q89" s="10" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="90" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H90" s="22"/>
+      <c r="L90" s="24"/>
+      <c r="M90" s="46"/>
+      <c r="Q90" s="10" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="91" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E91" s="8">
+        <v>78126</v>
+      </c>
+      <c r="F91" s="9"/>
+      <c r="G91" s="40"/>
+      <c r="H91" s="23"/>
+      <c r="I91" s="50">
+        <v>2036598</v>
+      </c>
+      <c r="K91" s="41"/>
+      <c r="L91" s="16"/>
+      <c r="M91" s="47">
+        <v>4074472</v>
+      </c>
+      <c r="N91" s="14"/>
+      <c r="O91" s="26"/>
+      <c r="P91" s="43"/>
+      <c r="Q91" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="R91" s="12"/>
+      <c r="S91" s="27"/>
+      <c r="T91" s="29"/>
+      <c r="U91" s="34">
+        <v>8142</v>
+      </c>
+      <c r="V91" s="38"/>
+      <c r="W91" s="32"/>
+      <c r="X91" s="31"/>
+    </row>
+    <row r="92" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E92" s="8">
+        <v>39142</v>
+      </c>
+      <c r="F92" s="9"/>
+      <c r="G92" s="40"/>
+      <c r="H92" s="23"/>
+      <c r="I92" s="50">
+        <v>6235501</v>
+      </c>
+      <c r="K92" s="41"/>
+      <c r="L92" s="16"/>
+      <c r="M92" s="47">
+        <v>1205582</v>
+      </c>
+      <c r="N92" s="14"/>
+      <c r="O92" s="26"/>
+      <c r="Q92" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="R92" s="12"/>
+      <c r="S92" s="27"/>
+      <c r="T92" s="29"/>
+      <c r="U92" s="34">
+        <v>4193</v>
+      </c>
+      <c r="V92" s="38"/>
+      <c r="W92" s="32"/>
+      <c r="X92" s="31"/>
+    </row>
+    <row r="93" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E89" s="8" t="s">
+      <c r="E93" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="F89" s="9"/>
-      <c r="G89" s="40"/>
-      <c r="H89" s="23"/>
-      <c r="I89" s="58">
+      <c r="F93" s="9"/>
+      <c r="G93" s="40"/>
+      <c r="H93" s="23"/>
+      <c r="I93" s="50">
         <v>1763432</v>
       </c>
-      <c r="K89" s="41"/>
-      <c r="L89" s="16"/>
-      <c r="M89" s="55">
+      <c r="K93" s="41"/>
+      <c r="L93" s="16"/>
+      <c r="M93" s="47">
         <v>9007303</v>
       </c>
-      <c r="N89" s="14"/>
-      <c r="O89" s="26"/>
-      <c r="P89" s="51"/>
-      <c r="Q89" t="s">
-        <v>233</v>
-      </c>
-      <c r="R89" s="12"/>
-      <c r="S89" s="27"/>
-      <c r="T89" s="29"/>
-      <c r="U89" s="34">
+      <c r="N93" s="14"/>
+      <c r="O93" s="26"/>
+      <c r="P93" s="43"/>
+      <c r="Q93" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="R93" s="12"/>
+      <c r="S93" s="27"/>
+      <c r="T93" s="29"/>
+      <c r="U93" s="34">
         <v>4074</v>
       </c>
-      <c r="V89" s="38"/>
-      <c r="W89" s="32"/>
-      <c r="X89" s="31"/>
-      <c r="Y89" s="43">
-        <v>920</v>
-      </c>
-      <c r="Z89" s="44"/>
-      <c r="AA89" s="45"/>
-      <c r="AB89" s="50"/>
-    </row>
-    <row r="90" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
+      <c r="V93" s="38"/>
+      <c r="W93" s="32"/>
+      <c r="X93" s="31"/>
+    </row>
+    <row r="94" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="E90" s="8">
+      <c r="E94" s="8">
         <v>76800</v>
       </c>
-      <c r="F90" s="9"/>
-      <c r="G90" s="40"/>
-      <c r="H90" s="23"/>
-      <c r="I90" s="58">
+      <c r="F94" s="9"/>
+      <c r="G94" s="40"/>
+      <c r="H94" s="23"/>
+      <c r="I94" s="50">
         <v>6017263</v>
       </c>
-      <c r="K90" s="41"/>
-      <c r="L90" s="16"/>
-      <c r="M90" s="55">
+      <c r="K94" s="41"/>
+      <c r="L94" s="16"/>
+      <c r="M94" s="47">
         <v>6264014</v>
       </c>
-      <c r="N90" s="14"/>
-      <c r="O90" s="26"/>
-      <c r="P90" s="51"/>
-      <c r="Q90" t="s">
-        <v>234</v>
-      </c>
-      <c r="R90" s="12"/>
-      <c r="S90" s="27"/>
-      <c r="T90" s="29"/>
-      <c r="U90" s="34">
+      <c r="N94" s="14"/>
+      <c r="O94" s="26"/>
+      <c r="P94" s="43"/>
+      <c r="Q94" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="R94" s="12"/>
+      <c r="S94" s="27"/>
+      <c r="T94" s="29"/>
+      <c r="U94" s="34">
         <v>4050</v>
       </c>
-      <c r="V90" s="38"/>
-      <c r="W90" s="32"/>
-      <c r="X90" s="31"/>
-      <c r="Y90" s="43">
-        <v>931</v>
-      </c>
-      <c r="Z90" s="44"/>
-      <c r="AA90" s="45"/>
-      <c r="AB90" s="50"/>
-    </row>
-    <row r="91" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="I91" s="60"/>
-      <c r="L91" s="24"/>
-      <c r="M91" s="54"/>
-      <c r="Q91" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="92" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="L92" s="24"/>
-      <c r="M92" s="54"/>
-    </row>
-    <row r="93" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="L93" s="24"/>
-      <c r="M93" s="54"/>
-    </row>
-    <row r="94" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="L94" s="24"/>
-      <c r="M94" s="54"/>
-    </row>
-    <row r="95" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="L95" s="24"/>
-      <c r="M95" s="54"/>
-    </row>
-    <row r="96" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="V94" s="38"/>
+      <c r="W94" s="32"/>
+      <c r="X94" s="31"/>
+    </row>
+    <row r="95" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E95" s="8">
+        <v>26054</v>
+      </c>
+      <c r="F95" s="9"/>
+      <c r="G95" s="40"/>
+      <c r="H95" s="23"/>
+      <c r="I95" s="50" t="s">
+        <v>239</v>
+      </c>
+      <c r="K95" s="41"/>
+      <c r="L95" s="16"/>
+      <c r="M95" s="47">
+        <v>1028519</v>
+      </c>
+      <c r="N95" s="14"/>
+      <c r="O95" s="26"/>
+      <c r="P95" s="43"/>
+      <c r="Q95" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="R95" s="12"/>
+      <c r="S95" s="27"/>
+      <c r="T95" s="29"/>
+      <c r="V95" s="38"/>
+      <c r="W95" s="32"/>
+      <c r="X95" s="31"/>
+    </row>
+    <row r="96" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>135</v>
+      </c>
       <c r="L96" s="24"/>
-      <c r="M96" s="54"/>
+      <c r="M96" s="46"/>
+      <c r="Q96" s="10" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="97" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L97" s="24"/>
-      <c r="M97" s="54"/>
+      <c r="M97" s="46"/>
     </row>
     <row r="98" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L98" s="24"/>
-      <c r="M98" s="54"/>
+      <c r="M98" s="46"/>
     </row>
     <row r="99" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L99" s="24"/>
-      <c r="M99" s="54"/>
+      <c r="M99" s="46"/>
     </row>
     <row r="100" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L100" s="24"/>
-      <c r="M100" s="54"/>
+      <c r="M100" s="46"/>
     </row>
     <row r="101" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L101" s="24"/>
-      <c r="M101" s="54"/>
+      <c r="M101" s="46"/>
+    </row>
+    <row r="102" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L102" s="24"/>
+      <c r="M102" s="46"/>
+    </row>
+    <row r="103" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L103" s="24"/>
+      <c r="M103" s="46"/>
+    </row>
+    <row r="104" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L104" s="24"/>
+      <c r="M104" s="46"/>
+    </row>
+    <row r="105" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L105" s="24"/>
+      <c r="M105" s="46"/>
+    </row>
+    <row r="106" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L106" s="24"/>
+      <c r="M106" s="46"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:AB91">
-    <sortCondition ref="A3:A91"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:X96">
+    <sortCondition ref="A3:A96"/>
   </sortState>
-  <mergeCells count="9">
-    <mergeCell ref="Y1:AB1"/>
+  <mergeCells count="8">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:H1"/>

--- a/WorkBot/legacy/backend/pricing/Templates/IBProduce.xlsx
+++ b/WorkBot/legacy/backend/pricing/Templates/IBProduce.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andrew\Desktop\Andrew\Projects\IthacaBakery\RandomStuff\WorkBot\legacy\backend\pricing\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C26C4C2B-4CA9-42D3-BF42-89DA43FA1F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31586B23-9936-49AA-96D6-E0D29A77218A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7440" yWindow="3435" windowWidth="16200" windowHeight="9360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -579,9 +579,6 @@
     <t>PSPMX</t>
   </si>
   <si>
-    <t>PSPB10</t>
-  </si>
-  <si>
     <t>VCHARD</t>
   </si>
   <si>
@@ -754,6 +751,9 @@
   </si>
   <si>
     <t>PTOMSL</t>
+  </si>
+  <si>
+    <t>PSPB</t>
   </si>
 </sst>
 </file>
@@ -1664,7 +1664,7 @@
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D9"/>
       <c r="E9" s="54">
@@ -1683,7 +1683,7 @@
       <c r="O9" s="14"/>
       <c r="P9" s="14"/>
       <c r="Q9" s="51" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="R9" s="12"/>
       <c r="S9" s="12"/>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D10"/>
       <c r="E10" s="54">
@@ -1716,7 +1716,7 @@
       <c r="O10" s="14"/>
       <c r="P10" s="14"/>
       <c r="Q10" s="51" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="R10" s="12"/>
       <c r="S10" s="12"/>
@@ -1728,7 +1728,7 @@
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D11"/>
       <c r="E11" s="54"/>
@@ -1747,7 +1747,7 @@
       <c r="O11" s="14"/>
       <c r="P11" s="14"/>
       <c r="Q11" s="51" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="R11" s="12"/>
       <c r="S11" s="12"/>
@@ -1759,7 +1759,7 @@
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D12"/>
       <c r="E12" s="54">
@@ -1780,7 +1780,7 @@
       <c r="O12" s="14"/>
       <c r="P12" s="14"/>
       <c r="Q12" s="51" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="R12" s="12"/>
       <c r="S12" s="12"/>
@@ -2613,7 +2613,7 @@
       <c r="O44" s="26"/>
       <c r="P44" s="43"/>
       <c r="Q44" s="10" t="s">
-        <v>182</v>
+        <v>240</v>
       </c>
       <c r="R44" s="12"/>
       <c r="S44" s="27"/>
@@ -2669,7 +2669,7 @@
       <c r="L46" s="24"/>
       <c r="M46" s="46"/>
       <c r="Q46" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="R46" s="12"/>
       <c r="S46" s="27"/>
@@ -2702,7 +2702,7 @@
       <c r="O47" s="26"/>
       <c r="P47" s="43"/>
       <c r="Q47" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="R47" s="12"/>
       <c r="S47" s="27"/>
@@ -2731,7 +2731,7 @@
       <c r="L48" s="45"/>
       <c r="M48" s="46"/>
       <c r="Q48" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="R48" s="12"/>
       <c r="S48" s="27"/>
@@ -2764,7 +2764,7 @@
       <c r="O49" s="26"/>
       <c r="P49" s="43"/>
       <c r="Q49" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R49" s="12"/>
       <c r="S49" s="27"/>
@@ -2793,7 +2793,7 @@
       <c r="L50" s="16"/>
       <c r="M50" s="46"/>
       <c r="Q50" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="S50" s="27"/>
       <c r="T50" s="29"/>
@@ -2819,7 +2819,7 @@
       <c r="M51" s="46"/>
       <c r="O51" s="26"/>
       <c r="Q51" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R51" s="12"/>
       <c r="S51" s="27"/>
@@ -2848,7 +2848,7 @@
       <c r="L52" s="16"/>
       <c r="M52" s="46"/>
       <c r="Q52" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R52" s="12"/>
       <c r="S52" s="27"/>
@@ -2875,7 +2875,7 @@
       <c r="M53" s="46"/>
       <c r="O53" s="26"/>
       <c r="Q53" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="R53" s="12"/>
       <c r="S53" s="27"/>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="O54" s="26"/>
       <c r="Q54" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R54" s="12"/>
       <c r="S54" s="27"/>
@@ -2941,7 +2941,7 @@
       <c r="O55" s="26"/>
       <c r="P55" s="43"/>
       <c r="Q55" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="R55" s="12"/>
       <c r="S55" s="27"/>
@@ -2963,7 +2963,7 @@
       <c r="L56" s="24"/>
       <c r="M56" s="46"/>
       <c r="Q56" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="57" spans="1:24" x14ac:dyDescent="0.25">
@@ -2983,7 +2983,7 @@
       <c r="L57" s="24"/>
       <c r="M57" s="46"/>
       <c r="Q57" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R57" s="12"/>
       <c r="S57" s="27"/>
@@ -3017,7 +3017,7 @@
       <c r="O58" s="26"/>
       <c r="P58" s="43"/>
       <c r="Q58" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R58" s="12"/>
       <c r="S58" s="27"/>
@@ -3051,7 +3051,7 @@
       <c r="O59" s="26"/>
       <c r="P59" s="43"/>
       <c r="Q59" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="R59" s="12"/>
       <c r="S59" s="27"/>
@@ -3081,7 +3081,7 @@
       <c r="M60" s="46"/>
       <c r="O60" s="26"/>
       <c r="Q60" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="S60" s="27"/>
       <c r="T60" s="29"/>
@@ -3111,7 +3111,7 @@
       <c r="O61" s="26"/>
       <c r="P61" s="43"/>
       <c r="Q61" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="R61" s="12"/>
       <c r="S61" s="27"/>
@@ -3141,7 +3141,7 @@
       <c r="M62" s="46"/>
       <c r="O62" s="26"/>
       <c r="Q62" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="R62" s="12"/>
       <c r="S62" s="27"/>
@@ -3173,7 +3173,7 @@
       <c r="O63" s="26"/>
       <c r="P63" s="43"/>
       <c r="Q63" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="R63" s="12"/>
       <c r="S63" s="27"/>
@@ -3207,7 +3207,7 @@
       <c r="O64" s="26"/>
       <c r="P64" s="43"/>
       <c r="Q64" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S64" s="27"/>
       <c r="T64" s="29"/>
@@ -3238,7 +3238,7 @@
       <c r="O65" s="26"/>
       <c r="P65" s="43"/>
       <c r="Q65" s="10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="R65" s="12"/>
       <c r="S65" s="27"/>
@@ -3263,7 +3263,7 @@
       <c r="L66" s="24"/>
       <c r="M66" s="46"/>
       <c r="Q66" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="S66" s="27"/>
       <c r="T66" s="29"/>
@@ -3284,7 +3284,7 @@
       <c r="L67" s="24"/>
       <c r="M67" s="46"/>
       <c r="Q67" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="68" spans="1:24" x14ac:dyDescent="0.25">
@@ -3309,7 +3309,7 @@
       <c r="O68" s="26"/>
       <c r="P68" s="43"/>
       <c r="Q68" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="R68" s="12"/>
       <c r="S68" s="27"/>
@@ -3338,7 +3338,7 @@
       <c r="L69" s="16"/>
       <c r="M69" s="46"/>
       <c r="Q69" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="S69" s="27"/>
       <c r="T69" s="29"/>
@@ -3356,7 +3356,7 @@
       <c r="L70" s="24"/>
       <c r="M70" s="46"/>
       <c r="Q70" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="71" spans="1:24" x14ac:dyDescent="0.25">
@@ -3366,7 +3366,7 @@
       <c r="L71" s="24"/>
       <c r="M71" s="46"/>
       <c r="Q71" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="72" spans="1:24" x14ac:dyDescent="0.25">
@@ -3377,7 +3377,7 @@
       <c r="L72" s="24"/>
       <c r="M72" s="46"/>
       <c r="Q72" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="S72" s="27"/>
       <c r="T72" s="29"/>
@@ -3404,7 +3404,7 @@
       <c r="N73" s="14"/>
       <c r="O73" s="26"/>
       <c r="Q73" s="10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="R73" s="12"/>
       <c r="S73" s="27"/>
@@ -3433,7 +3433,7 @@
       <c r="L74" s="16"/>
       <c r="M74" s="46"/>
       <c r="Q74" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="R74" s="12"/>
       <c r="S74" s="27"/>
@@ -3464,7 +3464,7 @@
       <c r="O75" s="26"/>
       <c r="P75" s="43"/>
       <c r="Q75" s="52" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R75" s="12"/>
       <c r="S75" s="27"/>
@@ -3498,7 +3498,7 @@
       <c r="O76" s="26"/>
       <c r="P76" s="43"/>
       <c r="Q76" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R76" s="12"/>
       <c r="S76" s="27"/>
@@ -3532,7 +3532,7 @@
       <c r="O77" s="26"/>
       <c r="P77" s="43"/>
       <c r="Q77" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="R77" s="12"/>
       <c r="S77" s="27"/>
@@ -3566,7 +3566,7 @@
       <c r="O78" s="26"/>
       <c r="P78" s="43"/>
       <c r="Q78" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="S78" s="27"/>
       <c r="T78" s="29"/>
@@ -3594,7 +3594,7 @@
       <c r="L79" s="16"/>
       <c r="M79" s="46"/>
       <c r="Q79" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="S79" s="27"/>
       <c r="T79" s="29"/>
@@ -3644,7 +3644,7 @@
       <c r="O81" s="26"/>
       <c r="P81" s="43"/>
       <c r="Q81" s="10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="R81" s="12"/>
       <c r="S81" s="27"/>
@@ -3666,7 +3666,7 @@
       <c r="L82" s="24"/>
       <c r="M82" s="46"/>
       <c r="Q82" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R82" s="12"/>
       <c r="S82" s="27"/>
@@ -3714,7 +3714,7 @@
       <c r="M84" s="46"/>
       <c r="O84" s="26"/>
       <c r="Q84" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="R84" s="12"/>
       <c r="S84" s="27"/>
@@ -3748,7 +3748,7 @@
       <c r="O85" s="26"/>
       <c r="P85" s="43"/>
       <c r="Q85" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="R85" s="12"/>
       <c r="S85" s="27"/>
@@ -3778,7 +3778,7 @@
       <c r="M86" s="46"/>
       <c r="O86" s="26"/>
       <c r="Q86" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="S86" s="27"/>
       <c r="T86" s="29"/>
@@ -3793,7 +3793,7 @@
       <c r="L87" s="24"/>
       <c r="M87" s="46"/>
       <c r="Q87" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="88" spans="1:24" x14ac:dyDescent="0.25">
@@ -3812,7 +3812,7 @@
       <c r="L88" s="16"/>
       <c r="M88" s="46"/>
       <c r="Q88" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="R88" s="12"/>
       <c r="S88" s="27"/>
@@ -3828,7 +3828,7 @@
       <c r="L89" s="24"/>
       <c r="M89" s="46"/>
       <c r="Q89" s="10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="90" spans="1:24" x14ac:dyDescent="0.25">
@@ -3839,7 +3839,7 @@
       <c r="L90" s="24"/>
       <c r="M90" s="46"/>
       <c r="Q90" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="91" spans="1:24" x14ac:dyDescent="0.25">
@@ -3864,7 +3864,7 @@
       <c r="O91" s="26"/>
       <c r="P91" s="43"/>
       <c r="Q91" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="R91" s="12"/>
       <c r="S91" s="27"/>
@@ -3897,7 +3897,7 @@
       <c r="N92" s="14"/>
       <c r="O92" s="26"/>
       <c r="Q92" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="R92" s="12"/>
       <c r="S92" s="27"/>
@@ -3931,7 +3931,7 @@
       <c r="O93" s="26"/>
       <c r="P93" s="43"/>
       <c r="Q93" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="R93" s="12"/>
       <c r="S93" s="27"/>
@@ -3965,7 +3965,7 @@
       <c r="O94" s="26"/>
       <c r="P94" s="43"/>
       <c r="Q94" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="R94" s="12"/>
       <c r="S94" s="27"/>
@@ -3979,7 +3979,7 @@
     </row>
     <row r="95" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E95" s="8">
         <v>26054</v>
@@ -3988,7 +3988,7 @@
       <c r="G95" s="40"/>
       <c r="H95" s="23"/>
       <c r="I95" s="50" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K95" s="41"/>
       <c r="L95" s="16"/>
@@ -3999,7 +3999,7 @@
       <c r="O95" s="26"/>
       <c r="P95" s="43"/>
       <c r="Q95" s="10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="R95" s="12"/>
       <c r="S95" s="27"/>
@@ -4015,7 +4015,7 @@
       <c r="L96" s="24"/>
       <c r="M96" s="46"/>
       <c r="Q96" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="97" spans="12:13" x14ac:dyDescent="0.25">
